--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12439.97</v>
+        <v>12989.34</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2266.17</v>
+        <v>2366.25</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>873.73</v>
+        <v>912.3099999999999</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6190.3</v>
+        <v>6463.67</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2499.16</v>
+        <v>2609.53</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22123.41</v>
+        <v>23100.43</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1891.15</v>
+        <v>1974.66</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>822.41</v>
+        <v>858.73</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14972.22</v>
+        <v>15633.42</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>19439.17</v>
+        <v>20297.64</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4642.12</v>
+        <v>4847.13</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3809.75</v>
+        <v>3977.99</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10073.71</v>
+        <v>10518.58</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1683.65</v>
+        <v>1758.01</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2046.61</v>
+        <v>2136.99</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1562.43</v>
+        <v>1631.43</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7651.29</v>
+        <v>7989.19</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2959.66</v>
+        <v>3090.36</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4360.4</v>
+        <v>4552.97</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5746.81</v>
+        <v>6000.6</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2429.66</v>
+        <v>2536.96</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6033.11</v>
+        <v>6299.54</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>11350.4</v>
+        <v>11851.66</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7663.61</v>
+        <v>8002.05</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>873.46</v>
+        <v>912.04</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5542.39</v>
+        <v>5787.15</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2297.62</v>
+        <v>2399.09</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3227.65</v>
+        <v>3370.19</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>989.5599999999999</v>
+        <v>1033.26</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2806.24</v>
+        <v>2930.17</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2964.97</v>
+        <v>3095.91</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4155.55</v>
+        <v>4339.07</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2057.05</v>
+        <v>2147.89</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5598.89</v>
+        <v>5846.15</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4249.05</v>
+        <v>4436.69</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3361.62</v>
+        <v>3510.08</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9269.42</v>
+        <v>9678.780000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7424.38</v>
+        <v>7752.25</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2197.15</v>
+        <v>2260.97</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3404.27</v>
+        <v>3503.16</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>52976.13</v>
+        <v>54514.9</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7138.12</v>
+        <v>7345.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7021.24</v>
+        <v>7225.18</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1213.53</v>
+        <v>1248.78</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3107.77</v>
+        <v>3198.04</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>919.64</v>
+        <v>946.35</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1376.3</v>
+        <v>1416.27</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1753.82</v>
+        <v>1804.76</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>31003.99</v>
+        <v>31904.54</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1738.42</v>
+        <v>1788.91</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28866.65</v>
+        <v>29705.12</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1613.2</v>
+        <v>1660.06</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2198.58</v>
+        <v>2262.44</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2246.15</v>
+        <v>2311.39</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>913.01</v>
+        <v>939.53</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2390.8</v>
+        <v>2460.24</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2537.02</v>
+        <v>2610.71</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3719.51</v>
+        <v>3827.55</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11061.63</v>
+        <v>11382.93</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3631.63</v>
+        <v>3737.11</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3212.17</v>
+        <v>3305.48</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6638.06</v>
+        <v>6830.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2030.71</v>
+        <v>2089.7</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>17615.77</v>
+        <v>18127.44</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3254.57</v>
+        <v>3349.11</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>774.88</v>
+        <v>797.39</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7379.11</v>
+        <v>7593.45</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6423.61</v>
+        <v>6610.2</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3399.03</v>
+        <v>3497.76</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2135.71</v>
+        <v>2197.75</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2584.79</v>
+        <v>2659.87</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11837.41</v>
+        <v>12181.24</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3421.68</v>
+        <v>3521.07</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1143.15</v>
+        <v>1176.36</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>6531.17</v>
+        <v>6720.88</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3564.33</v>
+        <v>3667.87</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7675.88</v>
+        <v>7898.84</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>14823.08</v>
+        <v>15253.64</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>6472.19</v>
+        <v>6660.18</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3413.12</v>
+        <v>3512.26</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7003.07</v>
+        <v>7030.68</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10404.4</v>
+        <v>10445.42</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1521.61</v>
+        <v>1527.61</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2959.13</v>
+        <v>2970.8</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4234.7</v>
+        <v>4251.4</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1343.97</v>
+        <v>1349.27</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>5485.12</v>
+        <v>5506.74</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7489.44</v>
+        <v>7518.97</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1462.17</v>
+        <v>1467.94</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6191.34</v>
+        <v>6215.75</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2534.33</v>
+        <v>2544.32</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3335.01</v>
+        <v>3348.16</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2789.83</v>
+        <v>2800.83</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6411.1</v>
+        <v>6436.38</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1680.05</v>
+        <v>1686.68</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3236.74</v>
+        <v>3249.5</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4809.38</v>
+        <v>4828.34</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3418.38</v>
+        <v>3431.86</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3835.45</v>
+        <v>3850.58</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6296.8</v>
+        <v>6321.63</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5609.18</v>
+        <v>5631.29</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>842.63</v>
+        <v>845.95</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1872.47</v>
+        <v>1879.85</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2101.45</v>
+        <v>2109.73</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5053.6</v>
+        <v>5073.52</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7674.74</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>20148.02</v>
+        <v>20227.46</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1956.51</v>
+        <v>1964.23</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12965.13</v>
+        <v>13016.24</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>837.91</v>
+        <v>841.21</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7012.54</v>
+        <v>7040.19</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>232026.89</v>
+        <v>232941.66</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>16385.07</v>
+        <v>16449.67</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>19519.07</v>
+        <v>19596.02</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8259.57</v>
+        <v>8292.129999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11727.02</v>
+        <v>11773.26</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>22439.53</v>
+        <v>22528</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2892.92</v>
+        <v>2904.33</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1653.69</v>
+        <v>1660.21</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>10485.81</v>
+        <v>10527.15</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>9097.42</v>
+        <v>9133.290000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2282.18</v>
+        <v>2291.18</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9634.1</v>
+        <v>9672.09</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1750.7</v>
+        <v>1757.6</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7685.28</v>
+        <v>7715.58</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5207.84</v>
+        <v>5228.37</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5852.41</v>
+        <v>5875.49</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5118.42</v>
+        <v>5138.6</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2186.98</v>
+        <v>2195.6</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1875.97</v>
+        <v>1883.36</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>5823.51</v>
+        <v>5846.47</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1560.54</v>
+        <v>1566.69</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5574.03</v>
+        <v>5596.01</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1281.74</v>
+        <v>1286.79</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3169.14</v>
+        <v>3181.63</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2275.22</v>
+        <v>2284.19</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2398.69</v>
+        <v>2438.22</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>768.9299999999999</v>
+        <v>781.61</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1122.08</v>
+        <v>1140.57</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6554.88</v>
+        <v>6662.91</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>771.63</v>
+        <v>784.35</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4463.94</v>
+        <v>4537.51</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>769.76</v>
+        <v>782.45</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2374.52</v>
+        <v>2413.66</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2154.06</v>
+        <v>2189.56</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3004.91</v>
+        <v>3054.43</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2398.82</v>
+        <v>2438.36</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>26805.4</v>
+        <v>27247.19</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>4403.93</v>
+        <v>4476.51</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>9271.08</v>
+        <v>9423.879999999999</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4168.76</v>
+        <v>4237.47</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>17377.48</v>
+        <v>17663.88</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6658.11</v>
+        <v>6767.84</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3928.57</v>
+        <v>3993.32</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>7255.99</v>
+        <v>7375.58</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>15052.98</v>
+        <v>15301.07</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2204.3</v>
+        <v>2240.63</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1640.76</v>
+        <v>1667.8</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1648.14</v>
+        <v>1675.3</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4552.57</v>
+        <v>4627.6</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2738.63</v>
+        <v>2783.77</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>4557.72</v>
+        <v>4632.84</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>18106.99</v>
+        <v>18405.42</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>839.03</v>
+        <v>852.86</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2349.44</v>
+        <v>2388.17</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5006.2</v>
+        <v>5088.71</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3207.22</v>
+        <v>3260.08</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7392.6</v>
+        <v>7514.44</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2214.2</v>
+        <v>2250.69</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>832.6</v>
+        <v>846.33</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>920.84</v>
+        <v>936.02</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2617.13</v>
+        <v>2660.26</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>966</v>
+        <v>981.9299999999999</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>23697.7</v>
+        <v>24088.27</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2292.21</v>
+        <v>2329.99</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1740.31</v>
+        <v>1768.99</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1517.62</v>
+        <v>1542.64</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6797.89</v>
+        <v>6909.93</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1037.92</v>
+        <v>1055.03</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2836.25</v>
+        <v>2882.99</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2786.5</v>
+        <v>2832.42</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3793.97</v>
+        <v>3856.5</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1479.24</v>
+        <v>1503.62</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4656.91</v>
+        <v>4733.66</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>8286.51</v>
+        <v>8423.08</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>10051.8</v>
+        <v>10217.47</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>15833.31</v>
+        <v>16094.26</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>17383.91</v>
+        <v>17670.42</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6265.17</v>
+        <v>6368.43</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2542.52</v>
+        <v>2584.42</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1646.22</v>
+        <v>1673.36</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>75100.27</v>
+        <v>76338.03</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2443.21</v>
+        <v>2449.22</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>890.8</v>
+        <v>892.99</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5983.73</v>
+        <v>5998.45</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2394.71</v>
+        <v>2400.6</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1041.32</v>
+        <v>1043.88</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>884.63</v>
+        <v>886.8</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2484.38</v>
+        <v>2490.5</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2302.2</v>
+        <v>2307.86</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>24177.35</v>
+        <v>24236.84</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2739.15</v>
+        <v>2745.89</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2651.59</v>
+        <v>2658.12</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2456.66</v>
+        <v>2462.7</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2449.27</v>
+        <v>2455.29</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4246.37</v>
+        <v>4256.81</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2078.95</v>
+        <v>2084.07</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5394.92</v>
+        <v>5408.19</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2325.17</v>
+        <v>2330.89</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1493.12</v>
+        <v>1496.8</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1970.18</v>
+        <v>1975.03</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>154380.5</v>
+        <v>154760.34</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2337.96</v>
+        <v>2343.71</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1449.77</v>
+        <v>1453.34</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>30441.73</v>
+        <v>30516.63</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>9857.459999999999</v>
+        <v>9881.709999999999</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>61714.63</v>
+        <v>61866.47</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7309.94</v>
+        <v>7327.93</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2781.68</v>
+        <v>2788.53</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2391</v>
+        <v>2396.89</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10180.61</v>
+        <v>10205.66</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3360.9</v>
+        <v>3369.17</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3800.22</v>
+        <v>3809.57</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4423.13</v>
+        <v>4434.02</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>18247.17</v>
+        <v>18292.07</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>9699.23</v>
+        <v>9723.1</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2782.97</v>
+        <v>2789.81</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7638.3</v>
+        <v>7657.1</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1209.81</v>
+        <v>1212.79</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4652.81</v>
+        <v>4592.91</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4475.52</v>
+        <v>4417.9</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6006.94</v>
+        <v>5929.6</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3926.2</v>
+        <v>3875.66</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1023.13</v>
+        <v>1009.95</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4661.08</v>
+        <v>4601.07</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>12894.05</v>
+        <v>12728.05</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>30047.63</v>
+        <v>29660.79</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3529.71</v>
+        <v>3484.26</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4887.66</v>
+        <v>4824.74</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3215.2</v>
+        <v>3173.81</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1181.59</v>
+        <v>1166.37</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4983.35</v>
+        <v>4919.2</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2804.31</v>
+        <v>2768.21</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1035.07</v>
+        <v>1021.75</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>770.4</v>
+        <v>760.48</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1807.45</v>
+        <v>1784.18</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1369.12</v>
+        <v>1351.49</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>4677.25</v>
+        <v>4617.03</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2947.7</v>
+        <v>2909.75</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>5718.09</v>
+        <v>5644.48</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2189.74</v>
+        <v>2161.55</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3804.92</v>
+        <v>3755.93</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2369.06</v>
+        <v>2338.56</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>926.75</v>
+        <v>914.8200000000001</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3697</v>
+        <v>3649.41</v>
       </c>
     </row>
     <row r="257">
@@ -16132,7 +16132,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1453.1</v>
+        <v>1434.39</v>
       </c>
     </row>
     <row r="258">
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6140.85</v>
+        <v>6061.8</v>
       </c>
     </row>
     <row r="259">
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1427.63</v>
+        <v>1409.25</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>3089.74</v>
+        <v>3049.96</v>
       </c>
     </row>
     <row r="261">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>803</v>
+        <v>792.67</v>
       </c>
     </row>
     <row r="262">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1041.02</v>
+        <v>1027.62</v>
       </c>
     </row>
     <row r="263">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2500.45</v>
+        <v>2468.26</v>
       </c>
     </row>
     <row r="264">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3850.55</v>
+        <v>3800.97</v>
       </c>
     </row>
     <row r="265">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4854.22</v>
+        <v>4791.73</v>
       </c>
     </row>
     <row r="266">
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>21852.51</v>
+        <v>21571.18</v>
       </c>
     </row>
     <row r="267">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>4209.27</v>
+        <v>4155.08</v>
       </c>
     </row>
     <row r="268">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>8925.139999999999</v>
+        <v>8810.24</v>
       </c>
     </row>
     <row r="269">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>13853.36</v>
+        <v>13675.01</v>
       </c>
     </row>
     <row r="270">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3256.94</v>
+        <v>3215.01</v>
       </c>
     </row>
     <row r="271">
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>9319.200000000001</v>
+        <v>9199.23</v>
       </c>
     </row>
     <row r="272">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1572</v>
+        <v>1551.76</v>
       </c>
     </row>
     <row r="273">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1994.46</v>
+        <v>1968.79</v>
       </c>
     </row>
     <row r="274">
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1525.18</v>
+        <v>1505.54</v>
       </c>
     </row>
     <row r="275">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>806.49</v>
+        <v>796.11</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>8995.52</v>
+        <v>8879.709999999999</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2747.39</v>
+        <v>2712.02</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2160.38</v>
+        <v>2132.57</v>
       </c>
     </row>
     <row r="279">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5313.37</v>
+        <v>5244.97</v>
       </c>
     </row>
     <row r="280">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7946.16</v>
+        <v>7843.86</v>
       </c>
     </row>
     <row r="281">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>17786.53</v>
+        <v>17661.01</v>
       </c>
     </row>
     <row r="282">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1164.75</v>
+        <v>1156.53</v>
       </c>
     </row>
     <row r="283">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>7630.24</v>
+        <v>7576.39</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>12356.4</v>
+        <v>12269.2</v>
       </c>
     </row>
     <row r="285">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>18095.95</v>
+        <v>17968.24</v>
       </c>
     </row>
     <row r="286">
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1383.18</v>
+        <v>1373.42</v>
       </c>
     </row>
     <row r="287">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>852.1900000000001</v>
+        <v>846.1799999999999</v>
       </c>
     </row>
     <row r="288">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>416676.42</v>
+        <v>413735.91</v>
       </c>
     </row>
     <row r="289">
@@ -18088,7 +18088,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4114.56</v>
+        <v>4085.52</v>
       </c>
     </row>
     <row r="290">
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3351.03</v>
+        <v>3327.38</v>
       </c>
     </row>
     <row r="291">
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2091.55</v>
+        <v>2076.79</v>
       </c>
     </row>
     <row r="292">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>11189.93</v>
+        <v>11110.96</v>
       </c>
     </row>
     <row r="293">
@@ -18332,7 +18332,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1532.37</v>
+        <v>1521.55</v>
       </c>
     </row>
     <row r="294">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3131.02</v>
+        <v>3108.93</v>
       </c>
     </row>
     <row r="295">
@@ -18454,7 +18454,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>18209.28</v>
+        <v>18080.78</v>
       </c>
     </row>
     <row r="296">
@@ -18515,7 +18515,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2066.02</v>
+        <v>2051.44</v>
       </c>
     </row>
     <row r="297">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2087.92</v>
+        <v>2073.18</v>
       </c>
     </row>
     <row r="298">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3085.78</v>
+        <v>3064.01</v>
       </c>
     </row>
     <row r="299">
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>948.45</v>
+        <v>941.76</v>
       </c>
     </row>
     <row r="300">
@@ -18759,7 +18759,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>5390.42</v>
+        <v>5352.38</v>
       </c>
     </row>
     <row r="301">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>9645.08</v>
+        <v>9577.02</v>
       </c>
     </row>
     <row r="302">
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1178</v>
+        <v>1169.69</v>
       </c>
     </row>
     <row r="303">
@@ -18942,7 +18942,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1542.27</v>
+        <v>1531.39</v>
       </c>
     </row>
     <row r="304">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>36613.14</v>
+        <v>36354.76</v>
       </c>
     </row>
     <row r="305">
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>6563.28</v>
+        <v>6516.96</v>
       </c>
     </row>
     <row r="306">
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2454.19</v>
+        <v>2436.87</v>
       </c>
     </row>
     <row r="307">
@@ -19186,7 +19186,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3750.85</v>
+        <v>3724.38</v>
       </c>
     </row>
     <row r="308">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>967.03</v>
+        <v>960.21</v>
       </c>
     </row>
     <row r="309">
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>6321.93</v>
+        <v>6277.32</v>
       </c>
     </row>
     <row r="310">
@@ -19369,7 +19369,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>13943.43</v>
+        <v>13845.03</v>
       </c>
     </row>
     <row r="311">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2409.54</v>
+        <v>2392.54</v>
       </c>
     </row>
     <row r="312">
@@ -19491,7 +19491,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2078.82</v>
+        <v>2064.15</v>
       </c>
     </row>
     <row r="313">
@@ -19552,7 +19552,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>6170.31</v>
+        <v>6126.76</v>
       </c>
     </row>
     <row r="314">
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>11521.7</v>
+        <v>11440.39</v>
       </c>
     </row>
     <row r="315">
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>6947.75</v>
+        <v>6898.72</v>
       </c>
     </row>
     <row r="316">
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2993.01</v>
+        <v>2971.88</v>
       </c>
     </row>
     <row r="317">
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2017.61</v>
+        <v>2003.38</v>
       </c>
     </row>
     <row r="318">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>5119.26</v>
+        <v>5083.14</v>
       </c>
     </row>
     <row r="319">
@@ -19918,7 +19918,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>4993</v>
+        <v>4957.76</v>
       </c>
     </row>
     <row r="320">
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>984.77</v>
+        <v>977.8200000000001</v>
       </c>
     </row>
     <row r="321">
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>37626.72</v>
+        <v>37361.19</v>
       </c>
     </row>
     <row r="322">
@@ -20101,7 +20101,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>26406.36</v>
+        <v>26220.01</v>
       </c>
     </row>
     <row r="323">
@@ -20162,7 +20162,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3340.89</v>
+        <v>3317.32</v>
       </c>
     </row>
     <row r="324">
@@ -20223,7 +20223,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>6473.84</v>
+        <v>6428.15</v>
       </c>
     </row>
     <row r="325">
@@ -20284,7 +20284,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1098.75</v>
+        <v>1118.67</v>
       </c>
     </row>
     <row r="326">
@@ -20345,7 +20345,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>12437.22</v>
+        <v>12662.71</v>
       </c>
     </row>
     <row r="327">
@@ -20406,7 +20406,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1094.38</v>
+        <v>1114.22</v>
       </c>
     </row>
     <row r="328">
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2780.66</v>
+        <v>2831.07</v>
       </c>
     </row>
     <row r="329">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3946.48</v>
+        <v>4018.03</v>
       </c>
     </row>
     <row r="330">
@@ -20589,7 +20589,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2067.99</v>
+        <v>2105.48</v>
       </c>
     </row>
     <row r="331">
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1349.65</v>
+        <v>1374.12</v>
       </c>
     </row>
     <row r="332">
@@ -20711,7 +20711,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1906.43</v>
+        <v>1940.99</v>
       </c>
     </row>
     <row r="333">
@@ -20772,7 +20772,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2029.71</v>
+        <v>2066.51</v>
       </c>
     </row>
     <row r="334">
@@ -20833,7 +20833,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2200.75</v>
+        <v>2240.65</v>
       </c>
     </row>
     <row r="335">
@@ -20894,7 +20894,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2209.77</v>
+        <v>2249.83</v>
       </c>
     </row>
     <row r="336">
@@ -20955,7 +20955,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1355.03</v>
+        <v>1379.6</v>
       </c>
     </row>
     <row r="337">
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1252.1</v>
+        <v>1274.8</v>
       </c>
     </row>
     <row r="338">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>35921.44</v>
+        <v>36572.72</v>
       </c>
     </row>
     <row r="339">
@@ -21138,7 +21138,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>10057.6</v>
+        <v>10239.95</v>
       </c>
     </row>
     <row r="340">
@@ -21199,7 +21199,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3117.07</v>
+        <v>3173.58</v>
       </c>
     </row>
     <row r="341">
@@ -21260,7 +21260,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>5978.88</v>
+        <v>6087.28</v>
       </c>
     </row>
     <row r="342">
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>5117.86</v>
+        <v>5210.65</v>
       </c>
     </row>
     <row r="343">
@@ -21382,7 +21382,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1078.97</v>
+        <v>1098.54</v>
       </c>
     </row>
     <row r="344">
@@ -21443,7 +21443,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>966.92</v>
+        <v>984.45</v>
       </c>
     </row>
     <row r="345">
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>3646.24</v>
+        <v>3712.34</v>
       </c>
     </row>
     <row r="346">
@@ -21565,7 +21565,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2477.99</v>
+        <v>2522.92</v>
       </c>
     </row>
     <row r="347">
@@ -21626,7 +21626,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>10576.73</v>
+        <v>10768.5</v>
       </c>
     </row>
     <row r="348">
@@ -21687,7 +21687,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1270.6</v>
+        <v>1293.64</v>
       </c>
     </row>
     <row r="349">
@@ -21748,7 +21748,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>788.13</v>
+        <v>802.42</v>
       </c>
     </row>
     <row r="350">
@@ -21809,7 +21809,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>5777</v>
+        <v>5881.74</v>
       </c>
     </row>
     <row r="351">
@@ -21870,7 +21870,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1292.03</v>
+        <v>1315.46</v>
       </c>
     </row>
     <row r="352">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>14790.1</v>
+        <v>15058.26</v>
       </c>
     </row>
     <row r="353">
@@ -21992,7 +21992,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>21468.66</v>
+        <v>21857.9</v>
       </c>
     </row>
     <row r="354">
@@ -22053,7 +22053,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>844.5</v>
+        <v>859.8099999999999</v>
       </c>
     </row>
     <row r="355">
@@ -22114,7 +22114,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1850.88</v>
+        <v>1884.43</v>
       </c>
     </row>
     <row r="356">
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2794.73</v>
+        <v>2845.4</v>
       </c>
     </row>
     <row r="357">
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>4910.11</v>
+        <v>4999.13</v>
       </c>
     </row>
     <row r="358">
@@ -22297,7 +22297,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1074.41</v>
+        <v>1093.89</v>
       </c>
     </row>
     <row r="359">
@@ -22358,7 +22358,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>7667.18</v>
+        <v>7806.19</v>
       </c>
     </row>
     <row r="360">
@@ -22419,7 +22419,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>7580.27</v>
+        <v>7717.71</v>
       </c>
     </row>
     <row r="361">
@@ -22480,7 +22480,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>4242.28</v>
+        <v>4319.19</v>
       </c>
     </row>
     <row r="362">
@@ -22541,7 +22541,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1252.16</v>
+        <v>1274.86</v>
       </c>
     </row>
     <row r="363">
@@ -22602,7 +22602,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>7649.49</v>
+        <v>7788.18</v>
       </c>
     </row>
     <row r="364">
@@ -22663,7 +22663,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>6160.58</v>
+        <v>6272.28</v>
       </c>
     </row>
     <row r="365">
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1808.36</v>
+        <v>1841.15</v>
       </c>
     </row>
     <row r="366">
@@ -22785,7 +22785,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>9046.76</v>
+        <v>9210.790000000001</v>
       </c>
     </row>
     <row r="367">
@@ -22846,7 +22846,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>9565.02</v>
+        <v>9738.440000000001</v>
       </c>
     </row>
     <row r="368">
@@ -22907,7 +22907,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2401</v>
+        <v>2444.53</v>
       </c>
     </row>
     <row r="369">
@@ -22968,7 +22968,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1075.15</v>
+        <v>1094.65</v>
       </c>
     </row>
     <row r="370">
@@ -23029,7 +23029,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1318.18</v>
+        <v>1342.08</v>
       </c>
     </row>
     <row r="371">
@@ -23090,7 +23090,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1463.01</v>
+        <v>1489.53</v>
       </c>
     </row>
     <row r="372">
@@ -23151,7 +23151,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1207.87</v>
+        <v>1229.77</v>
       </c>
     </row>
     <row r="373">
@@ -23212,7 +23212,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3990.41</v>
+        <v>4062.76</v>
       </c>
     </row>
     <row r="374">
@@ -23273,7 +23273,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2315.69</v>
+        <v>2357.68</v>
       </c>
     </row>
     <row r="375">
@@ -23334,7 +23334,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2728.23</v>
+        <v>2777.7</v>
       </c>
     </row>
     <row r="376">
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>6668.8</v>
+        <v>6789.71</v>
       </c>
     </row>
     <row r="377">
@@ -23456,7 +23456,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>7486.48</v>
+        <v>7622.21</v>
       </c>
     </row>
     <row r="378">
@@ -23517,7 +23517,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>4583.65</v>
+        <v>4666.75</v>
       </c>
     </row>
     <row r="379">
@@ -23578,7 +23578,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>5901.78</v>
+        <v>6008.79</v>
       </c>
     </row>
     <row r="380">
@@ -23639,7 +23639,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2195.23</v>
+        <v>2235.04</v>
       </c>
     </row>
     <row r="381">
@@ -23700,7 +23700,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>3609.65</v>
+        <v>3666.2</v>
       </c>
     </row>
     <row r="382">
@@ -23761,7 +23761,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3600.02</v>
+        <v>3656.41</v>
       </c>
     </row>
     <row r="383">
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>879.5</v>
+        <v>893.28</v>
       </c>
     </row>
     <row r="384">
@@ -23883,7 +23883,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>29775.76</v>
+        <v>30242.19</v>
       </c>
     </row>
     <row r="385">
@@ -23944,7 +23944,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>3212.83</v>
+        <v>3263.16</v>
       </c>
     </row>
     <row r="386">
@@ -24005,7 +24005,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>75708.58</v>
+        <v>76894.50999999999</v>
       </c>
     </row>
     <row r="387">
@@ -24066,7 +24066,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>3410.49</v>
+        <v>3463.91</v>
       </c>
     </row>
     <row r="388">
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>6178.91</v>
+        <v>6275.7</v>
       </c>
     </row>
     <row r="389">
@@ -24188,7 +24188,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2957.87</v>
+        <v>3004.21</v>
       </c>
     </row>
     <row r="390">
@@ -24249,7 +24249,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>12638.01</v>
+        <v>12835.97</v>
       </c>
     </row>
     <row r="391">
@@ -24310,7 +24310,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>3302.49</v>
+        <v>3354.23</v>
       </c>
     </row>
     <row r="392">
@@ -24371,7 +24371,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1033.2</v>
+        <v>1049.38</v>
       </c>
     </row>
     <row r="393">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>3960.16</v>
+        <v>4022.19</v>
       </c>
     </row>
     <row r="394">
@@ -24493,7 +24493,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1700.26</v>
+        <v>1726.9</v>
       </c>
     </row>
     <row r="395">
@@ -24554,7 +24554,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>72724.99000000001</v>
+        <v>73864.19</v>
       </c>
     </row>
     <row r="396">
@@ -24615,7 +24615,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>11066.27</v>
+        <v>11239.62</v>
       </c>
     </row>
     <row r="397">
@@ -24676,7 +24676,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1019.74</v>
+        <v>1035.72</v>
       </c>
     </row>
     <row r="398">
@@ -24737,7 +24737,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1131.56</v>
+        <v>1149.29</v>
       </c>
     </row>
     <row r="399">
@@ -24798,7 +24798,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>8338.629999999999</v>
+        <v>8469.25</v>
       </c>
     </row>
     <row r="400">
@@ -24859,7 +24859,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>44534.95</v>
+        <v>45232.57</v>
       </c>
     </row>
     <row r="401">
@@ -24920,7 +24920,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>43111.19</v>
+        <v>43786.5</v>
       </c>
     </row>
     <row r="402">
@@ -24981,7 +24981,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>4001.49</v>
+        <v>4064.17</v>
       </c>
     </row>
     <row r="403">
@@ -25042,7 +25042,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>7902</v>
+        <v>8025.79</v>
       </c>
     </row>
     <row r="404">
@@ -25103,7 +25103,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>5859.27</v>
+        <v>5951.05</v>
       </c>
     </row>
     <row r="405">
@@ -25168,7 +25168,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>323276</v>
+        <v>328339.96</v>
       </c>
     </row>
     <row r="406">
@@ -25229,7 +25229,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>3314.08</v>
+        <v>3365.99</v>
       </c>
     </row>
     <row r="407">
@@ -25290,7 +25290,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3869.69</v>
+        <v>3930.31</v>
       </c>
     </row>
     <row r="408">
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>8116.93</v>
+        <v>8244.08</v>
       </c>
     </row>
     <row r="409">
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>7749.67</v>
+        <v>7871.06</v>
       </c>
     </row>
     <row r="410">
@@ -25473,7 +25473,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>4556.02</v>
+        <v>4627.39</v>
       </c>
     </row>
     <row r="411">
@@ -25534,7 +25534,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2071.95</v>
+        <v>2104.4</v>
       </c>
     </row>
     <row r="412">
@@ -25595,7 +25595,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>5871.35</v>
+        <v>5963.32</v>
       </c>
     </row>
     <row r="413">
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>11162.44</v>
+        <v>11337.3</v>
       </c>
     </row>
     <row r="414">
@@ -25717,7 +25717,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2312.07</v>
+        <v>2348.28</v>
       </c>
     </row>
     <row r="415">
@@ -25778,7 +25778,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3840.22</v>
+        <v>3900.37</v>
       </c>
     </row>
     <row r="416">
@@ -25839,7 +25839,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2759.13</v>
+        <v>2802.35</v>
       </c>
     </row>
     <row r="417">
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>32540.74</v>
+        <v>33050.47</v>
       </c>
     </row>
     <row r="418">
@@ -25961,7 +25961,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>843.98</v>
+        <v>857.2</v>
       </c>
     </row>
     <row r="419">
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1283.56</v>
+        <v>1303.67</v>
       </c>
     </row>
     <row r="420">
@@ -26083,7 +26083,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2743.87</v>
+        <v>2786.85</v>
       </c>
     </row>
     <row r="421">
@@ -26144,7 +26144,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>8108.29</v>
+        <v>8235.299999999999</v>
       </c>
     </row>
     <row r="422">
@@ -26205,7 +26205,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>989.88</v>
+        <v>1005.39</v>
       </c>
     </row>
     <row r="423">
@@ -26266,7 +26266,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>6374.18</v>
+        <v>6474.03</v>
       </c>
     </row>
     <row r="424">
@@ -26327,7 +26327,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2328.7</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="425">
@@ -26388,7 +26388,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2741.24</v>
+        <v>2741.1</v>
       </c>
     </row>
     <row r="426">
@@ -26449,7 +26449,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1006.82</v>
+        <v>1006.77</v>
       </c>
     </row>
     <row r="427">
@@ -26510,7 +26510,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>14682.21</v>
+        <v>14681.45</v>
       </c>
     </row>
     <row r="428">
@@ -26571,7 +26571,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>5874.51</v>
+        <v>5874.21</v>
       </c>
     </row>
     <row r="429">
@@ -26632,7 +26632,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1283.56</v>
+        <v>1283.49</v>
       </c>
     </row>
     <row r="430">
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>768.33</v>
+        <v>768.29</v>
       </c>
     </row>
     <row r="431">
@@ -26754,7 +26754,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1168.08</v>
+        <v>1168.02</v>
       </c>
     </row>
     <row r="432">
@@ -26815,7 +26815,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1751.66</v>
+        <v>1751.57</v>
       </c>
     </row>
     <row r="433">
@@ -26876,7 +26876,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>7201.25</v>
+        <v>7200.88</v>
       </c>
     </row>
     <row r="434">
@@ -26937,7 +26937,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>18422.58</v>
+        <v>18421.63</v>
       </c>
     </row>
     <row r="435">
@@ -26998,7 +26998,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>23447.06</v>
+        <v>23445.85</v>
       </c>
     </row>
     <row r="436">
@@ -27059,7 +27059,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>965.6799999999999</v>
+        <v>965.63</v>
       </c>
     </row>
     <row r="437">
@@ -27120,7 +27120,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>6368.8</v>
+        <v>6368.47</v>
       </c>
     </row>
     <row r="438">
@@ -27181,7 +27181,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>2131.27</v>
+        <v>2131.16</v>
       </c>
     </row>
     <row r="439">
@@ -27242,7 +27242,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>905.24</v>
+        <v>905.2</v>
       </c>
     </row>
     <row r="440">
@@ -27303,7 +27303,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>769.11</v>
+        <v>769.0700000000001</v>
       </c>
     </row>
     <row r="441">
@@ -27364,7 +27364,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2205.55</v>
+        <v>2205.44</v>
       </c>
     </row>
     <row r="442">
@@ -27425,7 +27425,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>775.17</v>
+        <v>775.13</v>
       </c>
     </row>
     <row r="443">
@@ -27486,7 +27486,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>8735.52</v>
+        <v>8735.07</v>
       </c>
     </row>
     <row r="444">
@@ -27547,7 +27547,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>33900.63</v>
+        <v>33898.89</v>
       </c>
     </row>
     <row r="445">
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2365.35</v>
+        <v>2365.23</v>
       </c>
     </row>
     <row r="446">
@@ -27669,7 +27669,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>3796.84</v>
+        <v>3796.64</v>
       </c>
     </row>
     <row r="447">
@@ -27730,7 +27730,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>826.53</v>
+        <v>826.49</v>
       </c>
     </row>
     <row r="448">
@@ -27791,7 +27791,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>11616.81</v>
+        <v>11616.21</v>
       </c>
     </row>
     <row r="449">
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2588.32</v>
+        <v>2588.19</v>
       </c>
     </row>
     <row r="450">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>968.15</v>
+        <v>968.1</v>
       </c>
     </row>
     <row r="451">
@@ -27974,7 +27974,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>1888.65</v>
+        <v>1888.56</v>
       </c>
     </row>
     <row r="452">
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1307.88</v>
+        <v>1307.81</v>
       </c>
     </row>
     <row r="453">
@@ -28096,7 +28096,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2427.36</v>
+        <v>2427.24</v>
       </c>
     </row>
     <row r="454">
@@ -28157,7 +28157,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2982.65</v>
+        <v>2982.49</v>
       </c>
     </row>
     <row r="455">
@@ -28218,7 +28218,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>9602.809999999999</v>
+        <v>9602.309999999999</v>
       </c>
     </row>
     <row r="456">
@@ -28279,7 +28279,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>803.7</v>
+        <v>803.66</v>
       </c>
     </row>
     <row r="457">
@@ -28340,7 +28340,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2978.32</v>
+        <v>2978.17</v>
       </c>
     </row>
     <row r="458">
@@ -28401,7 +28401,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>32951.44</v>
+        <v>32949.74</v>
       </c>
     </row>
     <row r="459">
@@ -28462,7 +28462,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>16064.89</v>
+        <v>16064.07</v>
       </c>
     </row>
     <row r="460">
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2482.03</v>
+        <v>2481.91</v>
       </c>
     </row>
     <row r="461">
@@ -28584,7 +28584,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>7582.11</v>
+        <v>7581.72</v>
       </c>
     </row>
     <row r="462">
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3076.54</v>
+        <v>3076.39</v>
       </c>
     </row>
     <row r="463">
@@ -28706,7 +28706,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>2649</v>
+        <v>2648.87</v>
       </c>
     </row>
     <row r="464">
@@ -28767,7 +28767,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>785.49</v>
+        <v>785.45</v>
       </c>
     </row>
     <row r="465">
@@ -28828,7 +28828,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>1437.49</v>
+        <v>1437.42</v>
       </c>
     </row>
     <row r="466">
@@ -28889,7 +28889,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1940.81</v>
+        <v>1940.71</v>
       </c>
     </row>
     <row r="467">
@@ -28950,7 +28950,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1396.38</v>
+        <v>1396.31</v>
       </c>
     </row>
     <row r="468">
@@ -29011,7 +29011,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>1510.16</v>
+        <v>1510.08</v>
       </c>
     </row>
     <row r="469">
@@ -29072,7 +29072,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>10207.3</v>
+        <v>10206.78</v>
       </c>
     </row>
     <row r="470">
@@ -29133,7 +29133,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1759.32</v>
+        <v>1759.23</v>
       </c>
     </row>
     <row r="471">
@@ -29194,7 +29194,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2445.15</v>
+        <v>2445.02</v>
       </c>
     </row>
     <row r="472">
@@ -29255,7 +29255,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1546.14</v>
+        <v>1546.06</v>
       </c>
     </row>
     <row r="473">
@@ -29316,7 +29316,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>3510.09</v>
+        <v>3509.91</v>
       </c>
     </row>
     <row r="474">
@@ -29377,7 +29377,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1200.4</v>
+        <v>1200.34</v>
       </c>
     </row>
     <row r="475">
@@ -29438,7 +29438,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>20631.5</v>
+        <v>20630.44</v>
       </c>
     </row>
     <row r="476">
@@ -29499,7 +29499,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1098.4</v>
+        <v>1098.34</v>
       </c>
     </row>
     <row r="477">
@@ -29560,7 +29560,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1591.9</v>
+        <v>1591.81</v>
       </c>
     </row>
     <row r="478">
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>10245.65</v>
+        <v>10245.13</v>
       </c>
     </row>
     <row r="479">
@@ -29682,7 +29682,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>6777.91</v>
+        <v>6777.56</v>
       </c>
     </row>
     <row r="480">
@@ -29743,7 +29743,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>7517.62</v>
+        <v>7517.23</v>
       </c>
     </row>
     <row r="481">
@@ -29804,7 +29804,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>870.01</v>
+        <v>869.96</v>
       </c>
     </row>
     <row r="482">
@@ -29865,7 +29865,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>5708.54</v>
+        <v>5708.24</v>
       </c>
     </row>
     <row r="483">
@@ -29926,7 +29926,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>11420.9</v>
+        <v>11420.32</v>
       </c>
     </row>
     <row r="484">
@@ -29987,7 +29987,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>20081.94</v>
+        <v>19992.14</v>
       </c>
     </row>
     <row r="485">
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>1859.97</v>
+        <v>1851.65</v>
       </c>
     </row>
     <row r="486">
@@ -30109,7 +30109,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>1887.61</v>
+        <v>1879.17</v>
       </c>
     </row>
     <row r="487">
@@ -30170,7 +30170,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>5582.62</v>
+        <v>5557.66</v>
       </c>
     </row>
     <row r="488">
@@ -30231,7 +30231,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>4448.75</v>
+        <v>4428.86</v>
       </c>
     </row>
     <row r="489">
@@ -30292,7 +30292,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>3579.3</v>
+        <v>3563.3</v>
       </c>
     </row>
     <row r="490">
@@ -30353,7 +30353,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>2447.51</v>
+        <v>2436.57</v>
       </c>
     </row>
     <row r="491">
@@ -30414,7 +30414,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>1098.37</v>
+        <v>1093.46</v>
       </c>
     </row>
     <row r="492">
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>4350.34</v>
+        <v>4330.89</v>
       </c>
     </row>
     <row r="493">
@@ -30536,7 +30536,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>3753.81</v>
+        <v>3737.02</v>
       </c>
     </row>
     <row r="494">
@@ -30597,7 +30597,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>1797.83</v>
+        <v>1789.79</v>
       </c>
     </row>
     <row r="495">
@@ -30658,7 +30658,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1518.69</v>
+        <v>1511.9</v>
       </c>
     </row>
     <row r="496">
@@ -30719,7 +30719,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>18179.06</v>
+        <v>18097.77</v>
       </c>
     </row>
     <row r="497">
@@ -30780,7 +30780,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>2023.67</v>
+        <v>2014.62</v>
       </c>
     </row>
     <row r="498">
@@ -30841,7 +30841,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>17002.25</v>
+        <v>16926.22</v>
       </c>
     </row>
     <row r="499">
@@ -30902,7 +30902,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1317.02</v>
+        <v>1311.13</v>
       </c>
     </row>
     <row r="500">
@@ -30963,7 +30963,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>6889.1</v>
+        <v>6858.3</v>
       </c>
     </row>
     <row r="501">
@@ -31024,7 +31024,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>3846.34</v>
+        <v>3829.14</v>
       </c>
     </row>
     <row r="502">
@@ -31085,7 +31085,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>1640.99</v>
+        <v>1633.65</v>
       </c>
     </row>
     <row r="503">
@@ -31146,7 +31146,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>53098.54</v>
+        <v>52861.11</v>
       </c>
     </row>
     <row r="504">
@@ -31207,7 +31207,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>2648.65</v>
+        <v>2636.81</v>
       </c>
     </row>
     <row r="505">
@@ -31268,7 +31268,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2717</v>
+        <v>2704.85</v>
       </c>
     </row>
     <row r="506">
@@ -31329,7 +31329,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>7182.16</v>
+        <v>7150.04</v>
       </c>
     </row>
     <row r="507">
@@ -31390,7 +31390,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2153.96</v>
+        <v>2144.33</v>
       </c>
     </row>
     <row r="508">
@@ -31451,7 +31451,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>2390.91</v>
+        <v>2380.21</v>
       </c>
     </row>
     <row r="509">
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1526.93</v>
+        <v>1520.1</v>
       </c>
     </row>
     <row r="510">
@@ -31573,7 +31573,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>1078.04</v>
+        <v>1073.22</v>
       </c>
     </row>
     <row r="511">
@@ -31634,7 +31634,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>6577.75</v>
+        <v>6548.34</v>
       </c>
     </row>
     <row r="512">
@@ -31695,7 +31695,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>843.8099999999999</v>
+        <v>840.04</v>
       </c>
     </row>
     <row r="513">
@@ -31756,7 +31756,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>1295.95</v>
+        <v>1290.16</v>
       </c>
     </row>
     <row r="514">
@@ -31817,7 +31817,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>4395.87</v>
+        <v>4376.22</v>
       </c>
     </row>
     <row r="515">
@@ -31878,7 +31878,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>4542.06</v>
+        <v>4521.75</v>
       </c>
     </row>
     <row r="516">
@@ -31939,7 +31939,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>6928.15</v>
+        <v>6897.17</v>
       </c>
     </row>
     <row r="517">
@@ -32000,7 +32000,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>1820.13</v>
+        <v>1811.99</v>
       </c>
     </row>
     <row r="518">
@@ -32061,7 +32061,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>6441.82</v>
+        <v>6413.02</v>
       </c>
     </row>
     <row r="519">
@@ -32122,7 +32122,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1141.15</v>
+        <v>1136.05</v>
       </c>
     </row>
     <row r="520">
@@ -32183,7 +32183,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1544.57</v>
+        <v>1537.66</v>
       </c>
     </row>
     <row r="521">
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2717.63</v>
+        <v>2705.47</v>
       </c>
     </row>
     <row r="522">
@@ -32305,7 +32305,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>1591.38</v>
+        <v>1584.26</v>
       </c>
     </row>
     <row r="523">
@@ -32366,7 +32366,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>6120.72</v>
+        <v>6093.35</v>
       </c>
     </row>
     <row r="524">
@@ -32427,7 +32427,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>2989.83</v>
+        <v>2976.46</v>
       </c>
     </row>
     <row r="525">
@@ -32488,7 +32488,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2523.34</v>
+        <v>2525.51</v>
       </c>
     </row>
     <row r="526">
@@ -32549,7 +32549,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>7710.59</v>
+        <v>7717.23</v>
       </c>
     </row>
     <row r="527">
@@ -32610,7 +32610,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1131.61</v>
+        <v>1132.59</v>
       </c>
     </row>
     <row r="528">
@@ -32671,7 +32671,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>10587.52</v>
+        <v>10596.64</v>
       </c>
     </row>
     <row r="529">
@@ -32732,7 +32732,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1387.55</v>
+        <v>1388.74</v>
       </c>
     </row>
     <row r="530">
@@ -32793,7 +32793,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>4223.56</v>
+        <v>4227.2</v>
       </c>
     </row>
     <row r="531">
@@ -32854,7 +32854,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>67526.53999999999</v>
+        <v>67584.71000000001</v>
       </c>
     </row>
     <row r="532">
@@ -32915,7 +32915,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1391.94</v>
+        <v>1393.13</v>
       </c>
     </row>
     <row r="533">
@@ -32976,7 +32976,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>44524.43</v>
+        <v>44562.79</v>
       </c>
     </row>
     <row r="534">
@@ -33037,7 +33037,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2260.44</v>
+        <v>2262.39</v>
       </c>
     </row>
     <row r="535">
@@ -33098,7 +33098,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>2197.75</v>
+        <v>2199.64</v>
       </c>
     </row>
     <row r="536">
@@ -33159,7 +33159,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1511.45</v>
+        <v>1512.75</v>
       </c>
     </row>
     <row r="537">
@@ -33220,7 +33220,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>4583.21</v>
+        <v>4587.16</v>
       </c>
     </row>
     <row r="538">
@@ -33281,7 +33281,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>8644.860000000001</v>
+        <v>8652.309999999999</v>
       </c>
     </row>
     <row r="539">
@@ -33342,7 +33342,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>6554.14</v>
+        <v>6559.78</v>
       </c>
     </row>
     <row r="540">
@@ -33403,7 +33403,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>4354.86</v>
+        <v>4358.62</v>
       </c>
     </row>
     <row r="541">
@@ -33464,7 +33464,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>989.02</v>
+        <v>989.87</v>
       </c>
     </row>
     <row r="542">
@@ -33525,7 +33525,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>11512.26</v>
+        <v>11522.18</v>
       </c>
     </row>
     <row r="543">
@@ -33586,7 +33586,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>5689.26</v>
+        <v>5694.16</v>
       </c>
     </row>
     <row r="544">
@@ -33647,7 +33647,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>775</v>
+        <v>775.67</v>
       </c>
     </row>
     <row r="545">
@@ -33708,7 +33708,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1569.65</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="546">
@@ -33769,7 +33769,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1880.93</v>
+        <v>1882.55</v>
       </c>
     </row>
     <row r="547">
@@ -33830,7 +33830,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>6807.34</v>
+        <v>6813.2</v>
       </c>
     </row>
     <row r="548">
@@ -33891,7 +33891,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>13716.69</v>
+        <v>13728.5</v>
       </c>
     </row>
     <row r="549">
@@ -33952,7 +33952,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1591.73</v>
+        <v>1593.1</v>
       </c>
     </row>
     <row r="550">
@@ -34013,7 +34013,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1698.17</v>
+        <v>1699.64</v>
       </c>
     </row>
     <row r="551">
@@ -34074,7 +34074,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>6692.26</v>
+        <v>6698.03</v>
       </c>
     </row>
     <row r="552">
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>8814.02</v>
+        <v>8821.620000000001</v>
       </c>
     </row>
     <row r="553">
@@ -34196,7 +34196,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>2530.98</v>
+        <v>2533.16</v>
       </c>
     </row>
     <row r="554">
@@ -34257,7 +34257,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>15285.45</v>
+        <v>15298.62</v>
       </c>
     </row>
     <row r="555">
@@ -34318,7 +34318,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>75071.13</v>
+        <v>75135.81</v>
       </c>
     </row>
     <row r="556">
@@ -34379,7 +34379,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>11371.49</v>
+        <v>11381.29</v>
       </c>
     </row>
     <row r="557">
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>5262.08</v>
+        <v>5266.61</v>
       </c>
     </row>
     <row r="558">
@@ -34501,7 +34501,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>10975.48</v>
+        <v>10984.93</v>
       </c>
     </row>
     <row r="559">
@@ -34562,7 +34562,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>14997.64</v>
+        <v>15010.56</v>
       </c>
     </row>
     <row r="560">
@@ -34623,7 +34623,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>3698.59</v>
+        <v>3701.77</v>
       </c>
     </row>
     <row r="561">
@@ -34684,7 +34684,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>4827.91</v>
+        <v>4832.07</v>
       </c>
     </row>
     <row r="562">
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>10436.61</v>
+        <v>10445.6</v>
       </c>
     </row>
     <row r="563">
@@ -34806,7 +34806,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>17609.31</v>
+        <v>17624.48</v>
       </c>
     </row>
     <row r="564">
@@ -34867,7 +34867,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>11812.92</v>
+        <v>11823.1</v>
       </c>
     </row>
     <row r="565">
@@ -34928,7 +34928,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>4484.86</v>
+        <v>4488.73</v>
       </c>
     </row>
     <row r="566">
@@ -34989,7 +34989,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>1415.27</v>
+        <v>1416.49</v>
       </c>
     </row>
     <row r="567">
@@ -35050,7 +35050,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>14152</v>
+        <v>14164.2</v>
       </c>
     </row>
     <row r="568">
@@ -35111,7 +35111,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>923.1</v>
+        <v>923.9</v>
       </c>
     </row>
     <row r="569">
@@ -35172,7 +35172,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>22705.86</v>
+        <v>22725.43</v>
       </c>
     </row>
     <row r="570">
@@ -35233,7 +35233,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>10211.54</v>
+        <v>10220.34</v>
       </c>
     </row>
     <row r="571">
@@ -35294,7 +35294,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>2162.14</v>
+        <v>2164.01</v>
       </c>
     </row>
     <row r="572">
@@ -35355,7 +35355,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>4110.46</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="573">
@@ -35416,7 +35416,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>6267.94</v>
+        <v>6273.34</v>
       </c>
     </row>
     <row r="574">
@@ -35477,7 +35477,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>10694.78</v>
+        <v>10703.99</v>
       </c>
     </row>
     <row r="575">
@@ -35538,7 +35538,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1403.06</v>
+        <v>1404.27</v>
       </c>
     </row>
     <row r="576">
@@ -35599,7 +35599,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>864.3</v>
+        <v>865.04</v>
       </c>
     </row>
     <row r="577">
@@ -35660,7 +35660,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>1242.91</v>
+        <v>1243.98</v>
       </c>
     </row>
     <row r="578">
@@ -35721,7 +35721,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>4122.66</v>
+        <v>4126.22</v>
       </c>
     </row>
     <row r="579">
@@ -35782,7 +35782,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>768.16</v>
+        <v>768.8200000000001</v>
       </c>
     </row>
     <row r="580">
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>768.62</v>
+        <v>769.28</v>
       </c>
     </row>
     <row r="581">
@@ -35904,7 +35904,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2707.24</v>
+        <v>2709.57</v>
       </c>
     </row>
     <row r="582">
@@ -35965,7 +35965,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>4358.88</v>
+        <v>4362.64</v>
       </c>
     </row>
     <row r="583">
@@ -36026,7 +36026,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>3247.25</v>
+        <v>3250.05</v>
       </c>
     </row>
     <row r="584">
@@ -36087,7 +36087,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>1352.95</v>
+        <v>1354.12</v>
       </c>
     </row>
     <row r="585">
@@ -36148,7 +36148,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1677.05</v>
+        <v>1683.98</v>
       </c>
     </row>
     <row r="586">
@@ -36209,7 +36209,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>6335.4</v>
+        <v>6361.57</v>
       </c>
     </row>
     <row r="587">
@@ -36270,7 +36270,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2092.55</v>
+        <v>2101.2</v>
       </c>
     </row>
     <row r="588">
@@ -36331,7 +36331,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1320.37</v>
+        <v>1325.82</v>
       </c>
     </row>
     <row r="589">
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2779.17</v>
+        <v>2790.65</v>
       </c>
     </row>
     <row r="590">
@@ -36453,7 +36453,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>45961.33</v>
+        <v>46151.19</v>
       </c>
     </row>
     <row r="591">
@@ -36514,7 +36514,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>4574.84</v>
+        <v>4593.74</v>
       </c>
     </row>
     <row r="592">
@@ -36575,7 +36575,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>14151.47</v>
+        <v>14209.93</v>
       </c>
     </row>
     <row r="593">
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>6310.31</v>
+        <v>6336.38</v>
       </c>
     </row>
     <row r="594">
@@ -36697,7 +36697,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>817.35</v>
+        <v>820.73</v>
       </c>
     </row>
     <row r="595">
@@ -36758,7 +36758,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2198.09</v>
+        <v>2207.17</v>
       </c>
     </row>
     <row r="596">
@@ -36819,7 +36819,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>3123.7</v>
+        <v>3136.6</v>
       </c>
     </row>
     <row r="597">
@@ -36880,7 +36880,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>3794.57</v>
+        <v>3810.25</v>
       </c>
     </row>
     <row r="598">
@@ -36941,7 +36941,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>2966.07</v>
+        <v>2978.32</v>
       </c>
     </row>
     <row r="599">
@@ -37002,7 +37002,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>956.1</v>
+        <v>960.05</v>
       </c>
     </row>
     <row r="600">
@@ -37063,7 +37063,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>3070.45</v>
+        <v>3083.14</v>
       </c>
     </row>
     <row r="601">
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>16482.24</v>
+        <v>16550.33</v>
       </c>
     </row>
     <row r="602">
@@ -37185,7 +37185,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>40755.22</v>
+        <v>40923.57</v>
       </c>
     </row>
     <row r="603">
@@ -37246,7 +37246,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>4067.4</v>
+        <v>4084.2</v>
       </c>
     </row>
     <row r="604">
@@ -37307,7 +37307,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>9469.459999999999</v>
+        <v>9508.57</v>
       </c>
     </row>
     <row r="605">
@@ -37368,7 +37368,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>7202.37</v>
+        <v>7232.12</v>
       </c>
     </row>
     <row r="606">
@@ -37429,7 +37429,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>1296.07</v>
+        <v>1301.42</v>
       </c>
     </row>
     <row r="607">
@@ -37490,7 +37490,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1698.71</v>
+        <v>1705.73</v>
       </c>
     </row>
     <row r="608">
@@ -37551,7 +37551,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>793.25</v>
+        <v>796.52</v>
       </c>
     </row>
     <row r="609">
@@ -37612,7 +37612,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>3205.6</v>
+        <v>3218.84</v>
       </c>
     </row>
     <row r="610">
@@ -37673,7 +37673,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>1645.96</v>
+        <v>1652.76</v>
       </c>
     </row>
     <row r="611">
@@ -37734,7 +37734,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>5587.12</v>
+        <v>5610.2</v>
       </c>
     </row>
     <row r="612">
@@ -37795,7 +37795,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>6336.7</v>
+        <v>6362.88</v>
       </c>
     </row>
     <row r="613">
@@ -37856,7 +37856,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>15380.54</v>
+        <v>15444.08</v>
       </c>
     </row>
     <row r="614">
@@ -37917,7 +37917,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>1334.53</v>
+        <v>1340.04</v>
       </c>
     </row>
     <row r="615">
@@ -37978,7 +37978,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>4390.81</v>
+        <v>4408.95</v>
       </c>
     </row>
     <row r="616">
@@ -38039,7 +38039,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>2412.98</v>
+        <v>2422.94</v>
       </c>
     </row>
     <row r="617">
@@ -38100,7 +38100,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>2518.2</v>
+        <v>2528.6</v>
       </c>
     </row>
     <row r="618">
@@ -38161,7 +38161,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>7121.54</v>
+        <v>7150.96</v>
       </c>
     </row>
     <row r="619">
@@ -38222,7 +38222,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>10812.43</v>
+        <v>10857.1</v>
       </c>
     </row>
     <row r="620">
@@ -38283,7 +38283,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>792.92</v>
+        <v>796.2</v>
       </c>
     </row>
     <row r="621">
@@ -38344,7 +38344,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>3919.61</v>
+        <v>3935.81</v>
       </c>
     </row>
     <row r="622">
@@ -38405,7 +38405,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>1395.84</v>
+        <v>1401.61</v>
       </c>
     </row>
     <row r="623">
@@ -38466,7 +38466,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>6022.59</v>
+        <v>6047.47</v>
       </c>
     </row>
     <row r="624">
@@ -38527,7 +38527,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>21333.88</v>
+        <v>21422.01</v>
       </c>
     </row>
     <row r="625">
@@ -38588,7 +38588,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>1549.82</v>
+        <v>1556.22</v>
       </c>
     </row>
     <row r="626">
@@ -38649,7 +38649,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>2699.56</v>
+        <v>2710.71</v>
       </c>
     </row>
     <row r="627">
@@ -38710,7 +38710,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>1646.3</v>
+        <v>1653.1</v>
       </c>
     </row>
     <row r="628">
@@ -38771,7 +38771,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>1555.68</v>
+        <v>1562.11</v>
       </c>
     </row>
     <row r="629">
@@ -38832,7 +38832,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2147.26</v>
+        <v>2141.34</v>
       </c>
     </row>
     <row r="630">
@@ -38893,7 +38893,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2143.63</v>
+        <v>2137.71</v>
       </c>
     </row>
     <row r="631">
@@ -38954,7 +38954,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>1758.36</v>
+        <v>1753.51</v>
       </c>
     </row>
     <row r="632">
@@ -39015,7 +39015,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>3793.32</v>
+        <v>3782.86</v>
       </c>
     </row>
     <row r="633">
@@ -39076,7 +39076,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>3294.03</v>
+        <v>3284.95</v>
       </c>
     </row>
     <row r="634">
@@ -39137,7 +39137,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>841.33</v>
+        <v>839.01</v>
       </c>
     </row>
     <row r="635">
@@ -39198,7 +39198,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>1872.56</v>
+        <v>1867.4</v>
       </c>
     </row>
     <row r="636">
@@ -39259,7 +39259,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>1106.16</v>
+        <v>1103.11</v>
       </c>
     </row>
     <row r="637">
@@ -39320,7 +39320,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>4078.95</v>
+        <v>4067.7</v>
       </c>
     </row>
     <row r="638">
@@ -39385,7 +39385,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>139.98</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="639">
@@ -39446,7 +39446,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>7214.73</v>
+        <v>7194.83</v>
       </c>
     </row>
     <row r="640">
@@ -39507,7 +39507,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>1271.03</v>
+        <v>1267.52</v>
       </c>
     </row>
     <row r="641">
@@ -39568,7 +39568,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>11909.54</v>
+        <v>11876.69</v>
       </c>
     </row>
     <row r="642">
@@ -39629,7 +39629,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1853.16</v>
+        <v>1848.05</v>
       </c>
     </row>
     <row r="643">
@@ -39690,7 +39690,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3438.56</v>
+        <v>3429.08</v>
       </c>
     </row>
     <row r="644">
@@ -39751,7 +39751,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>2504.6</v>
+        <v>2497.69</v>
       </c>
     </row>
     <row r="645">
@@ -39812,7 +39812,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>3509.46</v>
+        <v>3499.78</v>
       </c>
     </row>
     <row r="646">
@@ -39873,7 +39873,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>2003.36</v>
+        <v>1997.83</v>
       </c>
     </row>
     <row r="647">
@@ -39934,7 +39934,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>16567.79</v>
+        <v>16522.09</v>
       </c>
     </row>
     <row r="648">
@@ -39995,7 +39995,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>2352.6</v>
+        <v>2346.11</v>
       </c>
     </row>
     <row r="649">
@@ -40056,7 +40056,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>6041.17</v>
+        <v>6024.5</v>
       </c>
     </row>
     <row r="650">
@@ -40117,7 +40117,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>794.64</v>
+        <v>792.45</v>
       </c>
     </row>
     <row r="651">
@@ -40178,7 +40178,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1726.26</v>
+        <v>1721.5</v>
       </c>
     </row>
     <row r="652">
@@ -40239,7 +40239,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>4901.92</v>
+        <v>4888.4</v>
       </c>
     </row>
     <row r="653">
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>9528.190000000001</v>
+        <v>9501.9</v>
       </c>
     </row>
     <row r="654">
@@ -40361,7 +40361,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2242.39</v>
+        <v>2236.21</v>
       </c>
     </row>
     <row r="655">
@@ -40422,7 +40422,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>3357.48</v>
+        <v>3348.21</v>
       </c>
     </row>
     <row r="656">
@@ -40483,7 +40483,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2313.96</v>
+        <v>2307.58</v>
       </c>
     </row>
     <row r="657">
@@ -40544,7 +40544,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>896.4</v>
+        <v>893.92</v>
       </c>
     </row>
     <row r="658">
@@ -40605,7 +40605,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>8737.9</v>
+        <v>8713.790000000001</v>
       </c>
     </row>
     <row r="659">
@@ -40666,7 +40666,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1658.34</v>
+        <v>1653.76</v>
       </c>
     </row>
     <row r="660">
@@ -40727,7 +40727,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>3307.91</v>
+        <v>3298.78</v>
       </c>
     </row>
     <row r="661">
@@ -40788,7 +40788,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>2642.41</v>
+        <v>2635.12</v>
       </c>
     </row>
     <row r="662">
@@ -40849,7 +40849,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>1686.86</v>
+        <v>1682.21</v>
       </c>
     </row>
     <row r="663">
@@ -40910,7 +40910,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>1294.43</v>
+        <v>1290.86</v>
       </c>
     </row>
     <row r="664">
@@ -40971,7 +40971,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>5132.87</v>
+        <v>5118.71</v>
       </c>
     </row>
     <row r="665">
@@ -41032,7 +41032,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2950.71</v>
+        <v>2942.57</v>
       </c>
     </row>
     <row r="666">
@@ -41093,7 +41093,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>777.73</v>
+        <v>775.59</v>
       </c>
     </row>
     <row r="667">
@@ -41154,7 +41154,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>1413</v>
+        <v>1409.11</v>
       </c>
     </row>
     <row r="668">
@@ -41215,7 +41215,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>975.1799999999999</v>
+        <v>972.49</v>
       </c>
     </row>
     <row r="669">
@@ -41276,7 +41276,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>1614</v>
+        <v>1609.55</v>
       </c>
     </row>
     <row r="670">
@@ -41337,7 +41337,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>5172.41</v>
+        <v>5158.14</v>
       </c>
     </row>
     <row r="671">
@@ -41398,7 +41398,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>2304.99</v>
+        <v>2298.63</v>
       </c>
     </row>
     <row r="672">
@@ -41459,7 +41459,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>7226.54</v>
+        <v>7206.61</v>
       </c>
     </row>
     <row r="673">
@@ -41520,7 +41520,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>12887.88</v>
+        <v>12852.33</v>
       </c>
     </row>
     <row r="674">
@@ -41581,7 +41581,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>5899.26</v>
+        <v>5882.99</v>
       </c>
     </row>
     <row r="675">
@@ -41642,7 +41642,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>3955.91</v>
+        <v>3944.99</v>
       </c>
     </row>
     <row r="676">
@@ -41703,7 +41703,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2768.45</v>
+        <v>2760.81</v>
       </c>
     </row>
     <row r="677">
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>1216.45</v>
+        <v>1213.1</v>
       </c>
     </row>
     <row r="678">
@@ -41825,7 +41825,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>1246.82</v>
+        <v>1243.38</v>
       </c>
     </row>
     <row r="679">
@@ -41886,7 +41886,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>2663.91</v>
+        <v>2656.56</v>
       </c>
     </row>
     <row r="680">
@@ -41947,7 +41947,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>9198.110000000001</v>
+        <v>9172.74</v>
       </c>
     </row>
     <row r="681">
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>7367.46</v>
+        <v>7347.14</v>
       </c>
     </row>
     <row r="682">
@@ -42069,7 +42069,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>4093.56</v>
+        <v>4082.27</v>
       </c>
     </row>
     <row r="683">
@@ -42130,7 +42130,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1096.3</v>
+        <v>1093.28</v>
       </c>
     </row>
     <row r="684">
@@ -42191,7 +42191,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>3025.97</v>
+        <v>3017.62</v>
       </c>
     </row>
     <row r="685">
@@ -42252,7 +42252,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>12881.18</v>
+        <v>12845.64</v>
       </c>
     </row>
     <row r="686">
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>52188.24</v>
+        <v>52044.29</v>
       </c>
     </row>
     <row r="687">
@@ -42374,7 +42374,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1859.89</v>
+        <v>1854.76</v>
       </c>
     </row>
     <row r="688">
@@ -42435,7 +42435,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>987.4400000000001</v>
+        <v>976.05</v>
       </c>
     </row>
     <row r="689">
@@ -42496,7 +42496,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>787.11</v>
+        <v>778.03</v>
       </c>
     </row>
     <row r="690">
@@ -42557,7 +42557,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>5616.63</v>
+        <v>5551.79</v>
       </c>
     </row>
     <row r="691">
@@ -42618,7 +42618,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>12373.63</v>
+        <v>12230.79</v>
       </c>
     </row>
     <row r="692">
@@ -42679,7 +42679,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>1441.77</v>
+        <v>1425.12</v>
       </c>
     </row>
     <row r="693">
@@ -42740,7 +42740,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>1047.91</v>
+        <v>1035.81</v>
       </c>
     </row>
     <row r="694">
@@ -42801,7 +42801,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>6073.22</v>
+        <v>6003.11</v>
       </c>
     </row>
     <row r="695">
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>3331.74</v>
+        <v>3293.27</v>
       </c>
     </row>
     <row r="696">
@@ -42923,7 +42923,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2792.89</v>
+        <v>2760.65</v>
       </c>
     </row>
     <row r="697">
@@ -42984,7 +42984,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>13324.4</v>
+        <v>13170.58</v>
       </c>
     </row>
     <row r="698">
@@ -43045,7 +43045,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>3764.28</v>
+        <v>3720.82</v>
       </c>
     </row>
     <row r="699">
@@ -43106,7 +43106,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2089.28</v>
+        <v>2065.16</v>
       </c>
     </row>
     <row r="700">
@@ -43167,7 +43167,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>1893.84</v>
+        <v>1871.98</v>
       </c>
     </row>
     <row r="701">
@@ -43228,7 +43228,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1991.48</v>
+        <v>1968.49</v>
       </c>
     </row>
     <row r="702">
@@ -43289,7 +43289,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>872.8200000000001</v>
+        <v>862.74</v>
       </c>
     </row>
     <row r="703">
@@ -43350,7 +43350,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>1955.21</v>
+        <v>1932.64</v>
       </c>
     </row>
     <row r="704">
@@ -43411,7 +43411,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>16220.05</v>
+        <v>16032.8</v>
       </c>
     </row>
     <row r="705">
@@ -43472,7 +43472,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>7563.17</v>
+        <v>7475.86</v>
       </c>
     </row>
     <row r="706">
@@ -43533,7 +43533,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2587.55</v>
+        <v>2557.68</v>
       </c>
     </row>
     <row r="707">
@@ -43594,7 +43594,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>5970.91</v>
+        <v>5901.98</v>
       </c>
     </row>
     <row r="708">
@@ -43655,7 +43655,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>2311.9</v>
+        <v>2285.21</v>
       </c>
     </row>
     <row r="709">
@@ -43716,7 +43716,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>2308.75</v>
+        <v>2282.1</v>
       </c>
     </row>
     <row r="710">
@@ -43777,7 +43777,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>5855.88</v>
+        <v>5788.28</v>
       </c>
     </row>
     <row r="711">
@@ -43838,7 +43838,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>1648.26</v>
+        <v>1629.23</v>
       </c>
     </row>
     <row r="712">
@@ -43899,7 +43899,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>3505.45</v>
+        <v>3464.98</v>
       </c>
     </row>
     <row r="713">
@@ -43960,7 +43960,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1502.06</v>
+        <v>1484.72</v>
       </c>
     </row>
     <row r="714">
@@ -44021,7 +44021,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2465.77</v>
+        <v>2437.3</v>
       </c>
     </row>
     <row r="715">
@@ -44082,7 +44082,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>2176.19</v>
+        <v>2151.07</v>
       </c>
     </row>
     <row r="716">
@@ -44143,7 +44143,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>3981.74</v>
+        <v>3935.77</v>
       </c>
     </row>
     <row r="717">
@@ -44204,7 +44204,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>7668.24</v>
+        <v>7579.72</v>
       </c>
     </row>
     <row r="718">
@@ -44265,7 +44265,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>1152.69</v>
+        <v>1139.39</v>
       </c>
     </row>
     <row r="719">
@@ -44326,7 +44326,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>2436.8</v>
+        <v>2408.67</v>
       </c>
     </row>
     <row r="720">
@@ -44387,7 +44387,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>27441.98</v>
+        <v>27125.18</v>
       </c>
     </row>
     <row r="721">
@@ -44448,7 +44448,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>1177.88</v>
+        <v>1164.28</v>
       </c>
     </row>
     <row r="722">
@@ -44509,7 +44509,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>2620.16</v>
+        <v>2589.91</v>
       </c>
     </row>
     <row r="723">
@@ -44570,7 +44570,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>819.1799999999999</v>
+        <v>809.73</v>
       </c>
     </row>
     <row r="724">
@@ -44631,7 +44631,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>900.35</v>
+        <v>889.96</v>
       </c>
     </row>
     <row r="725">
@@ -44692,7 +44692,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>2957.4</v>
+        <v>2923.26</v>
       </c>
     </row>
     <row r="726">
@@ -44753,7 +44753,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>7651</v>
+        <v>7562.67</v>
       </c>
     </row>
     <row r="727">
@@ -44814,7 +44814,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>3558.65</v>
+        <v>3517.57</v>
       </c>
     </row>
     <row r="728">
@@ -44875,7 +44875,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>4109.27</v>
+        <v>4061.83</v>
       </c>
     </row>
     <row r="729">
@@ -44936,7 +44936,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>1542.58</v>
+        <v>1524.77</v>
       </c>
     </row>
     <row r="730">
@@ -44997,7 +44997,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>1303.39</v>
+        <v>1288.34</v>
       </c>
     </row>
     <row r="731">
@@ -45058,7 +45058,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>4804.29</v>
+        <v>4748.82</v>
       </c>
     </row>
     <row r="732">
@@ -45119,7 +45119,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>769.2</v>
+        <v>760.3200000000001</v>
       </c>
     </row>
     <row r="733">
@@ -45180,7 +45180,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>1606.32</v>
+        <v>1587.78</v>
       </c>
     </row>
     <row r="734">
@@ -45241,7 +45241,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>3414.07</v>
+        <v>3374.65</v>
       </c>
     </row>
     <row r="735">
@@ -45302,7 +45302,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>2411.81</v>
+        <v>2383.97</v>
       </c>
     </row>
     <row r="736">
@@ -45363,7 +45363,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>7568.68</v>
+        <v>7481.3</v>
       </c>
     </row>
     <row r="737">
@@ -45424,7 +45424,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>4275.18</v>
+        <v>4225.83</v>
       </c>
     </row>
     <row r="738">
@@ -45485,7 +45485,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>813.17</v>
+        <v>801.04</v>
       </c>
     </row>
     <row r="739">
@@ -45546,7 +45546,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>3553.63</v>
+        <v>3500.62</v>
       </c>
     </row>
     <row r="740">
@@ -45607,7 +45607,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>768.8</v>
+        <v>757.33</v>
       </c>
     </row>
     <row r="741">
@@ -45668,7 +45668,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>943.74</v>
+        <v>929.67</v>
       </c>
     </row>
     <row r="742">
@@ -45729,7 +45729,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>1322.9</v>
+        <v>1303.17</v>
       </c>
     </row>
     <row r="743">
@@ -45790,7 +45790,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1520.34</v>
+        <v>1497.67</v>
       </c>
     </row>
     <row r="744">
@@ -45851,7 +45851,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>5076.43</v>
+        <v>5000.71</v>
       </c>
     </row>
     <row r="745">
@@ -45912,7 +45912,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>1320</v>
+        <v>1300.31</v>
       </c>
     </row>
     <row r="746">
@@ -45973,7 +45973,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>6287.67</v>
+        <v>6193.89</v>
       </c>
     </row>
     <row r="747">
@@ -46034,7 +46034,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>1512.97</v>
+        <v>1490.41</v>
       </c>
     </row>
     <row r="748">
@@ -46095,7 +46095,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>1796.39</v>
+        <v>1769.6</v>
       </c>
     </row>
     <row r="749">
@@ -46156,7 +46156,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>2229.2</v>
+        <v>2195.95</v>
       </c>
     </row>
     <row r="750">
@@ -46217,7 +46217,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>3621.83</v>
+        <v>3567.81</v>
       </c>
     </row>
     <row r="751">
@@ -46278,7 +46278,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>2203.41</v>
+        <v>2170.54</v>
       </c>
     </row>
     <row r="752">
@@ -46339,7 +46339,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>3913.81</v>
+        <v>3855.44</v>
       </c>
     </row>
     <row r="753">
@@ -46400,7 +46400,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>3992.02</v>
+        <v>3932.47</v>
       </c>
     </row>
     <row r="754">
@@ -46461,7 +46461,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>2675.89</v>
+        <v>2635.98</v>
       </c>
     </row>
     <row r="755">
@@ -46522,7 +46522,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>14216.29</v>
+        <v>14004.25</v>
       </c>
     </row>
     <row r="756">
@@ -46583,7 +46583,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2760.67</v>
+        <v>2719.5</v>
       </c>
     </row>
     <row r="757">
@@ -46644,7 +46644,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>2532.05</v>
+        <v>2494.28</v>
       </c>
     </row>
     <row r="758">
@@ -46705,7 +46705,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>6788.4</v>
+        <v>6687.15</v>
       </c>
     </row>
     <row r="759">
@@ -46766,7 +46766,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>1170.92</v>
+        <v>1153.46</v>
       </c>
     </row>
     <row r="760">
@@ -46827,7 +46827,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2189.33</v>
+        <v>2156.68</v>
       </c>
     </row>
     <row r="761">
@@ -46888,7 +46888,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>6404.84</v>
+        <v>6309.31</v>
       </c>
     </row>
     <row r="762">
@@ -46949,7 +46949,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>784.17</v>
+        <v>772.48</v>
       </c>
     </row>
     <row r="763">
@@ -47010,7 +47010,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>4354.66</v>
+        <v>4289.71</v>
       </c>
     </row>
     <row r="764">
@@ -47071,7 +47071,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>852.8099999999999</v>
+        <v>840.09</v>
       </c>
     </row>
     <row r="765">
@@ -47132,7 +47132,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>1386.68</v>
+        <v>1365.99</v>
       </c>
     </row>
     <row r="766">
@@ -47193,7 +47193,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>20594.88</v>
+        <v>20287.7</v>
       </c>
     </row>
     <row r="767">
@@ -47254,7 +47254,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>10064.33</v>
+        <v>9914.219999999999</v>
       </c>
     </row>
     <row r="768">
@@ -47315,7 +47315,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>37665.96</v>
+        <v>37104.16</v>
       </c>
     </row>
     <row r="769">
@@ -47376,7 +47376,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>24593.31</v>
+        <v>24226.49</v>
       </c>
     </row>
     <row r="770">
@@ -47437,7 +47437,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>1344.99</v>
+        <v>1324.93</v>
       </c>
     </row>
     <row r="771">
@@ -47498,7 +47498,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>2112.19</v>
+        <v>2080.69</v>
       </c>
     </row>
     <row r="772">
@@ -47559,7 +47559,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>6679.32</v>
+        <v>6579.69</v>
       </c>
     </row>
     <row r="773">
@@ -47620,7 +47620,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>47408.65</v>
+        <v>46701.53</v>
       </c>
     </row>
     <row r="774">
@@ -47681,7 +47681,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>3419.48</v>
+        <v>3368.48</v>
       </c>
     </row>
     <row r="775">
@@ -47742,7 +47742,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>18999.13</v>
+        <v>18715.76</v>
       </c>
     </row>
     <row r="776">
@@ -47803,7 +47803,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>1154.21</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="777">
@@ -47864,7 +47864,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>3294.98</v>
+        <v>3245.83</v>
       </c>
     </row>
     <row r="778">
@@ -47925,7 +47925,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>4469.17</v>
+        <v>4402.51</v>
       </c>
     </row>
     <row r="779">
@@ -47986,7 +47986,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>8687.389999999999</v>
+        <v>8557.809999999999</v>
       </c>
     </row>
     <row r="780">
@@ -48047,7 +48047,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>3072.54</v>
+        <v>3026.71</v>
       </c>
     </row>
     <row r="781">
@@ -48108,7 +48108,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>26906.82</v>
+        <v>26505.5</v>
       </c>
     </row>
     <row r="782">
@@ -48169,7 +48169,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>5167.04</v>
+        <v>5089.97</v>
       </c>
     </row>
     <row r="783">
@@ -48230,7 +48230,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1842.02</v>
+        <v>1814.54</v>
       </c>
     </row>
     <row r="784">
@@ -48291,7 +48291,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>6772.08</v>
+        <v>6671.08</v>
       </c>
     </row>
     <row r="785">
@@ -48352,7 +48352,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>2209.88</v>
+        <v>2197.19</v>
       </c>
     </row>
     <row r="786">
@@ -48413,7 +48413,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>2532.09</v>
+        <v>2517.55</v>
       </c>
     </row>
     <row r="787">
@@ -48474,7 +48474,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>35321.38</v>
+        <v>35118.49</v>
       </c>
     </row>
     <row r="788">
@@ -48535,7 +48535,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>2637.32</v>
+        <v>2622.17</v>
       </c>
     </row>
     <row r="789">
@@ -48596,7 +48596,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>1150.9</v>
+        <v>1144.29</v>
       </c>
     </row>
     <row r="790">
@@ -48657,7 +48657,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>2618.25</v>
+        <v>2603.21</v>
       </c>
     </row>
     <row r="791">
@@ -48718,7 +48718,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>4228.39</v>
+        <v>4204.1</v>
       </c>
     </row>
     <row r="792">
@@ -48779,7 +48779,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>1123.1</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="793">
@@ -48840,7 +48840,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>770.47</v>
+        <v>766.04</v>
       </c>
     </row>
     <row r="794">
@@ -48901,7 +48901,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>5584.5</v>
+        <v>5552.42</v>
       </c>
     </row>
     <row r="795">
@@ -48962,7 +48962,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>1004.16</v>
+        <v>998.39</v>
       </c>
     </row>
     <row r="796">
@@ -49023,7 +49023,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>3041.55</v>
+        <v>3024.08</v>
       </c>
     </row>
     <row r="797">
@@ -49084,7 +49084,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>18565.59</v>
+        <v>18458.95</v>
       </c>
     </row>
     <row r="798">
@@ -49145,7 +49145,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>2426.32</v>
+        <v>2412.38</v>
       </c>
     </row>
     <row r="799">
@@ -49206,7 +49206,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>2378.68</v>
+        <v>2365.01</v>
       </c>
     </row>
     <row r="800">
@@ -49267,7 +49267,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>800.12</v>
+        <v>795.53</v>
       </c>
     </row>
     <row r="801">
@@ -49328,7 +49328,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>4309.12</v>
+        <v>4284.37</v>
       </c>
     </row>
     <row r="802">
@@ -49389,7 +49389,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>1146.84</v>
+        <v>1140.26</v>
       </c>
     </row>
     <row r="803">
@@ -49450,7 +49450,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>1388.37</v>
+        <v>1380.39</v>
       </c>
     </row>
     <row r="804">
@@ -49511,7 +49511,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>786.05</v>
+        <v>781.54</v>
       </c>
     </row>
     <row r="805">
@@ -49572,7 +49572,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>1270.76</v>
+        <v>1263.46</v>
       </c>
     </row>
     <row r="806">
@@ -49633,7 +49633,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>5461.29</v>
+        <v>5429.92</v>
       </c>
     </row>
     <row r="807">
@@ -49694,7 +49694,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>6110.52</v>
+        <v>6075.42</v>
       </c>
     </row>
     <row r="808">
@@ -49755,7 +49755,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>2666</v>
+        <v>2650.69</v>
       </c>
     </row>
     <row r="809">
@@ -49816,7 +49816,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>3350.96</v>
+        <v>3331.71</v>
       </c>
     </row>
     <row r="810">
@@ -49877,7 +49877,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>2887</v>
+        <v>2870.42</v>
       </c>
     </row>
     <row r="811">
@@ -49938,7 +49938,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>1864.01</v>
+        <v>1853.31</v>
       </c>
     </row>
     <row r="812">
@@ -49999,7 +49999,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>7804.35</v>
+        <v>7759.52</v>
       </c>
     </row>
     <row r="813">
@@ -50060,7 +50060,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>2382.56</v>
+        <v>2368.88</v>
       </c>
     </row>
     <row r="814">
@@ -50121,7 +50121,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>2922.51</v>
+        <v>2905.72</v>
       </c>
     </row>
     <row r="815">
@@ -50182,7 +50182,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>1886.83</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="816">
@@ -50243,7 +50243,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>1061.71</v>
+        <v>1055.61</v>
       </c>
     </row>
     <row r="817">
@@ -50304,7 +50304,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>2259.96</v>
+        <v>2246.98</v>
       </c>
     </row>
     <row r="818">
@@ -50365,7 +50365,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>4705.94</v>
+        <v>4678.91</v>
       </c>
     </row>
     <row r="819">
@@ -50426,7 +50426,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>1100.26</v>
+        <v>1093.94</v>
       </c>
     </row>
     <row r="820">
@@ -50487,7 +50487,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>3912.03</v>
+        <v>3889.56</v>
       </c>
     </row>
     <row r="821">
@@ -50548,7 +50548,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>8862.02</v>
+        <v>8811.110000000001</v>
       </c>
     </row>
     <row r="822">
@@ -50609,7 +50609,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>3172.62</v>
+        <v>3154.4</v>
       </c>
     </row>
     <row r="823">
@@ -50670,7 +50670,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>2318.03</v>
+        <v>2304.71</v>
       </c>
     </row>
     <row r="824">
@@ -50731,7 +50731,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>864.9299999999999</v>
+        <v>859.96</v>
       </c>
     </row>
     <row r="825">
@@ -50792,7 +50792,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>1631.77</v>
+        <v>1622.4</v>
       </c>
     </row>
     <row r="826">
@@ -50853,7 +50853,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>13353.36</v>
+        <v>13276.65</v>
       </c>
     </row>
     <row r="827">
@@ -50914,7 +50914,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>27885.23</v>
+        <v>27725.06</v>
       </c>
     </row>
     <row r="828">
@@ -50975,7 +50975,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>5455.81</v>
+        <v>5424.47</v>
       </c>
     </row>
     <row r="829">
@@ -51036,7 +51036,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>1318.39</v>
+        <v>1310.82</v>
       </c>
     </row>
     <row r="830">
@@ -51097,7 +51097,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>2265.36</v>
+        <v>2252.35</v>
       </c>
     </row>
     <row r="831">
@@ -51158,7 +51158,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>4496.37</v>
+        <v>4470.55</v>
       </c>
     </row>
     <row r="832">
@@ -51219,7 +51219,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>2418.47</v>
+        <v>2404.58</v>
       </c>
     </row>
     <row r="833">
@@ -51280,7 +51280,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>1418.88</v>
+        <v>1410.73</v>
       </c>
     </row>
     <row r="834">
@@ -51341,7 +51341,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>5692.62</v>
+        <v>5659.92</v>
       </c>
     </row>
     <row r="835">
@@ -51402,7 +51402,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>1743.23</v>
+        <v>1733.21</v>
       </c>
     </row>
     <row r="836">
@@ -51463,7 +51463,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>1713.8</v>
+        <v>1703.96</v>
       </c>
     </row>
     <row r="837">
@@ -51524,7 +51524,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>5991.49</v>
+        <v>5957.07</v>
       </c>
     </row>
     <row r="838">
@@ -51585,7 +51585,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>916.23</v>
+        <v>910.97</v>
       </c>
     </row>
     <row r="839">
@@ -51646,7 +51646,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>3666.09</v>
+        <v>3645.04</v>
       </c>
     </row>
     <row r="840">
@@ -51707,7 +51707,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>6709.11</v>
+        <v>6670.57</v>
       </c>
     </row>
     <row r="841">
@@ -51768,7 +51768,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>1147.51</v>
+        <v>1140.92</v>
       </c>
     </row>
     <row r="842">
@@ -51829,7 +51829,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>1595.79</v>
+        <v>1586.63</v>
       </c>
     </row>
     <row r="843">
@@ -51890,7 +51890,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>1035.85</v>
+        <v>1029.9</v>
       </c>
     </row>
     <row r="844">
@@ -51951,7 +51951,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>872.2</v>
+        <v>867.1900000000001</v>
       </c>
     </row>
     <row r="845">
@@ -52012,7 +52012,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>3259.28</v>
+        <v>3240.56</v>
       </c>
     </row>
     <row r="846">
@@ -52073,7 +52073,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>1363.21</v>
+        <v>1355.38</v>
       </c>
     </row>
     <row r="847">
@@ -52134,7 +52134,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>875.73</v>
+        <v>870.7</v>
       </c>
     </row>
     <row r="848">
@@ -52195,7 +52195,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>8091.53</v>
+        <v>8045.06</v>
       </c>
     </row>
     <row r="849">
@@ -52256,7 +52256,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>8451.33</v>
+        <v>8402.780000000001</v>
       </c>
     </row>
     <row r="850">
@@ -52317,7 +52317,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>1402.89</v>
+        <v>1394.83</v>
       </c>
     </row>
     <row r="851">
@@ -52378,7 +52378,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>4514.94</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="852">
@@ -52439,7 +52439,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>2357.54</v>
+        <v>2342.44</v>
       </c>
     </row>
     <row r="853">
@@ -52500,7 +52500,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>63365.13</v>
+        <v>62959.18</v>
       </c>
     </row>
     <row r="854">
@@ -52561,7 +52561,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>23327.95</v>
+        <v>23178.5</v>
       </c>
     </row>
     <row r="855">
@@ -52622,7 +52622,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>1206.49</v>
+        <v>1198.76</v>
       </c>
     </row>
     <row r="856">
@@ -52683,7 +52683,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>1242.19</v>
+        <v>1234.23</v>
       </c>
     </row>
     <row r="857">
@@ -52744,7 +52744,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>4057.62</v>
+        <v>4031.63</v>
       </c>
     </row>
     <row r="858">
@@ -52805,7 +52805,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>2182.14</v>
+        <v>2168.16</v>
       </c>
     </row>
     <row r="859">
@@ -52866,7 +52866,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>2608.12</v>
+        <v>2591.41</v>
       </c>
     </row>
     <row r="860">
@@ -52927,7 +52927,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>2039.83</v>
+        <v>2026.76</v>
       </c>
     </row>
     <row r="861">
@@ -52988,7 +52988,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>1596.04</v>
+        <v>1585.82</v>
       </c>
     </row>
     <row r="862">
@@ -53049,7 +53049,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>1174.38</v>
+        <v>1166.86</v>
       </c>
     </row>
     <row r="863">
@@ -53110,7 +53110,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>48259.51</v>
+        <v>47950.34</v>
       </c>
     </row>
     <row r="864">
@@ -53171,7 +53171,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>1253.31</v>
+        <v>1245.28</v>
       </c>
     </row>
     <row r="865">
@@ -53232,7 +53232,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>1315.78</v>
+        <v>1307.35</v>
       </c>
     </row>
     <row r="866">
@@ -53293,7 +53293,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>1624.69</v>
+        <v>1614.29</v>
       </c>
     </row>
     <row r="867">
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>8586.58</v>
+        <v>8531.57</v>
       </c>
     </row>
     <row r="868">
@@ -53415,7 +53415,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>1852.13</v>
+        <v>1840.26</v>
       </c>
     </row>
     <row r="869">
@@ -53476,7 +53476,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>1145.44</v>
+        <v>1138.1</v>
       </c>
     </row>
     <row r="870">
@@ -53537,7 +53537,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>1352.64</v>
+        <v>1343.97</v>
       </c>
     </row>
     <row r="871">
@@ -53598,7 +53598,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>1664.84</v>
+        <v>1654.17</v>
       </c>
     </row>
     <row r="872">
@@ -53659,7 +53659,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>13634.31</v>
+        <v>13546.96</v>
       </c>
     </row>
     <row r="873">
@@ -53720,7 +53720,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>1680.58</v>
+        <v>1669.81</v>
       </c>
     </row>
     <row r="874">
@@ -53781,7 +53781,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>2920.68</v>
+        <v>2901.97</v>
       </c>
     </row>
     <row r="875">
@@ -53842,7 +53842,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>773.28</v>
+        <v>768.33</v>
       </c>
     </row>
     <row r="876">
@@ -53903,7 +53903,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>5529.76</v>
+        <v>5494.33</v>
       </c>
     </row>
     <row r="877">
@@ -53964,7 +53964,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>2253.82</v>
+        <v>2239.38</v>
       </c>
     </row>
     <row r="878">
@@ -54025,7 +54025,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>8175.98</v>
+        <v>8123.61</v>
       </c>
     </row>
     <row r="879">
@@ -54086,7 +54086,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>2739.73</v>
+        <v>2722.18</v>
       </c>
     </row>
     <row r="880">
@@ -54147,7 +54147,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>2836.19</v>
+        <v>2818.02</v>
       </c>
     </row>
     <row r="881">
@@ -54208,7 +54208,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>2827.85</v>
+        <v>2809.73</v>
       </c>
     </row>
     <row r="882">
@@ -54269,7 +54269,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>1098.2</v>
+        <v>1091.16</v>
       </c>
     </row>
     <row r="883">
@@ -54330,7 +54330,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>769.73</v>
+        <v>764.8</v>
       </c>
     </row>
     <row r="884">
@@ -54391,7 +54391,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>6441.19</v>
+        <v>6399.93</v>
       </c>
     </row>
     <row r="885">
@@ -54452,7 +54452,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>4812.69</v>
+        <v>4781.86</v>
       </c>
     </row>
     <row r="886">
@@ -54513,7 +54513,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>8706.33</v>
+        <v>8650.549999999999</v>
       </c>
     </row>
     <row r="887">
@@ -54574,7 +54574,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>7716.29</v>
+        <v>7666.86</v>
       </c>
     </row>
     <row r="888">
@@ -54635,7 +54635,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>7371.3</v>
+        <v>7324.08</v>
       </c>
     </row>
     <row r="889">
@@ -54696,7 +54696,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>4720.02</v>
+        <v>4689.78</v>
       </c>
     </row>
     <row r="890">
@@ -54757,7 +54757,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>3042.92</v>
+        <v>3023.43</v>
       </c>
     </row>
     <row r="891">
@@ -54818,7 +54818,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>6396.27</v>
+        <v>6355.29</v>
       </c>
     </row>
     <row r="892">
@@ -54879,7 +54879,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>799.46</v>
+        <v>794.34</v>
       </c>
     </row>
     <row r="893">
@@ -54940,7 +54940,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>2028.65</v>
+        <v>2015.66</v>
       </c>
     </row>
     <row r="894">
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>1949.21</v>
+        <v>1936.73</v>
       </c>
     </row>
     <row r="895">
@@ -55062,7 +55062,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>4252.46</v>
+        <v>4225.22</v>
       </c>
     </row>
     <row r="896">
@@ -55123,7 +55123,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>769.16</v>
+        <v>764.23</v>
       </c>
     </row>
     <row r="897">
@@ -55184,7 +55184,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>11086.11</v>
+        <v>11015.09</v>
       </c>
     </row>
     <row r="898">
@@ -55245,7 +55245,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>3431.53</v>
+        <v>3409.55</v>
       </c>
     </row>
     <row r="899">
@@ -55306,7 +55306,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>3782.67</v>
+        <v>3758.43</v>
       </c>
     </row>
     <row r="900">
@@ -55367,7 +55367,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>1455.9</v>
+        <v>1446.57</v>
       </c>
     </row>
     <row r="901">
@@ -55428,7 +55428,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>1949.76</v>
+        <v>1937.27</v>
       </c>
     </row>
     <row r="902">
@@ -55489,7 +55489,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>3943.16</v>
+        <v>3917.89</v>
       </c>
     </row>
     <row r="903">
@@ -55550,7 +55550,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>9414.389999999999</v>
+        <v>9354.08</v>
       </c>
     </row>
     <row r="904">
@@ -55611,7 +55611,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>1222.32</v>
+        <v>1214.49</v>
       </c>
     </row>
     <row r="905">
@@ -55672,7 +55672,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>7991.67</v>
+        <v>7940.47</v>
       </c>
     </row>
     <row r="906">
@@ -55733,7 +55733,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>1955.78</v>
+        <v>1943.25</v>
       </c>
     </row>
     <row r="907">
@@ -55794,7 +55794,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>2613.52</v>
+        <v>2596.78</v>
       </c>
     </row>
     <row r="908">
@@ -55855,7 +55855,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>792.23</v>
+        <v>787.15</v>
       </c>
     </row>
     <row r="909">
@@ -55916,7 +55916,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>768.72</v>
+        <v>765.4</v>
       </c>
     </row>
     <row r="910">
@@ -55977,7 +55977,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>5035.52</v>
+        <v>5013.83</v>
       </c>
     </row>
     <row r="911">
@@ -56038,7 +56038,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>4939.52</v>
+        <v>4918.24</v>
       </c>
     </row>
     <row r="912">
@@ -56099,7 +56099,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>1276.6</v>
+        <v>1271.1</v>
       </c>
     </row>
     <row r="913">
@@ -56160,7 +56160,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>5324.57</v>
+        <v>5301.63</v>
       </c>
     </row>
     <row r="914">
@@ -56221,7 +56221,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>1069.98</v>
+        <v>1065.37</v>
       </c>
     </row>
     <row r="915">
@@ -56282,7 +56282,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>1369.51</v>
+        <v>1363.61</v>
       </c>
     </row>
     <row r="916">
@@ -56343,7 +56343,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>2930.81</v>
+        <v>2918.18</v>
       </c>
     </row>
     <row r="917">
@@ -56404,7 +56404,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>3412.56</v>
+        <v>3397.86</v>
       </c>
     </row>
     <row r="918">
@@ -56465,7 +56465,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>1146.07</v>
+        <v>1141.13</v>
       </c>
     </row>
     <row r="919">
@@ -56526,7 +56526,7 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>3041.02</v>
+        <v>3027.92</v>
       </c>
     </row>
     <row r="920">
@@ -56587,7 +56587,7 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>1007.56</v>
+        <v>1003.22</v>
       </c>
     </row>
     <row r="921">
@@ -56648,7 +56648,7 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>1200.81</v>
+        <v>1195.64</v>
       </c>
     </row>
     <row r="922">
@@ -56709,7 +56709,7 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>1262.76</v>
+        <v>1257.32</v>
       </c>
     </row>
     <row r="923">
@@ -56770,7 +56770,7 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>773.98</v>
+        <v>770.65</v>
       </c>
     </row>
     <row r="924">
@@ -56831,7 +56831,7 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>20637.81</v>
+        <v>20548.9</v>
       </c>
     </row>
     <row r="925">
@@ -56892,7 +56892,7 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>3365.39</v>
+        <v>3350.89</v>
       </c>
     </row>
     <row r="926">
@@ -56953,7 +56953,7 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>2115.82</v>
+        <v>2106.71</v>
       </c>
     </row>
     <row r="927">
@@ -57014,7 +57014,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>2758.51</v>
+        <v>2746.62</v>
       </c>
     </row>
     <row r="928">
@@ -57075,7 +57075,7 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>4512.79</v>
+        <v>4493.35</v>
       </c>
     </row>
     <row r="929">
@@ -57136,7 +57136,7 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>786.3</v>
+        <v>782.91</v>
       </c>
     </row>
     <row r="930">
@@ -57197,7 +57197,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>2490.28</v>
+        <v>2479.55</v>
       </c>
     </row>
     <row r="931">
@@ -57258,7 +57258,7 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>5089.19</v>
+        <v>5067.27</v>
       </c>
     </row>
     <row r="932">
@@ -57319,7 +57319,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>9527.129999999999</v>
+        <v>9486.09</v>
       </c>
     </row>
     <row r="933">
@@ -57380,7 +57380,7 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>5922.02</v>
+        <v>5896.51</v>
       </c>
     </row>
     <row r="934">
@@ -57441,7 +57441,7 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>771.09</v>
+        <v>767.77</v>
       </c>
     </row>
     <row r="935">
@@ -57502,7 +57502,7 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>37365.34</v>
+        <v>37204.37</v>
       </c>
     </row>
     <row r="936">
@@ -57563,7 +57563,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>2991.96</v>
+        <v>2979.07</v>
       </c>
     </row>
     <row r="937">
@@ -57624,7 +57624,7 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>2198.75</v>
+        <v>2189.28</v>
       </c>
     </row>
     <row r="938">
@@ -57685,7 +57685,7 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>1711.72</v>
+        <v>1704.35</v>
       </c>
     </row>
     <row r="939">
@@ -57746,7 +57746,7 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>9660.93</v>
+        <v>9619.309999999999</v>
       </c>
     </row>
     <row r="940">
@@ -57807,7 +57807,7 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>15974.83</v>
+        <v>15906.01</v>
       </c>
     </row>
     <row r="941">
@@ -57868,7 +57868,7 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>2660.79</v>
+        <v>2649.32</v>
       </c>
     </row>
     <row r="942">
@@ -57929,7 +57929,7 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>3767</v>
+        <v>3750.77</v>
       </c>
     </row>
     <row r="943">
@@ -57990,7 +57990,7 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>2325.42</v>
+        <v>2315.4</v>
       </c>
     </row>
     <row r="944">
@@ -58051,7 +58051,7 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>2030.05</v>
+        <v>2021.31</v>
       </c>
     </row>
     <row r="945">
@@ -58112,7 +58112,7 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>17419.66</v>
+        <v>17344.62</v>
       </c>
     </row>
     <row r="946">
@@ -58173,7 +58173,7 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
-        <v>7290.91</v>
+        <v>7259.5</v>
       </c>
     </row>
     <row r="947">
@@ -58234,7 +58234,7 @@
         </is>
       </c>
       <c r="M947" s="2" t="n">
-        <v>4475.71</v>
+        <v>4456.43</v>
       </c>
     </row>
     <row r="948">
@@ -58295,7 +58295,7 @@
         </is>
       </c>
       <c r="M948" s="2" t="n">
-        <v>1916.26</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="949">
@@ -58356,7 +58356,7 @@
         </is>
       </c>
       <c r="M949" s="2" t="n">
-        <v>1784.35</v>
+        <v>1776.67</v>
       </c>
     </row>
     <row r="950">
@@ -58417,7 +58417,7 @@
         </is>
       </c>
       <c r="M950" s="2" t="n">
-        <v>1682.09</v>
+        <v>1674.84</v>
       </c>
     </row>
     <row r="951">
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="M951" s="2" t="n">
-        <v>780.96</v>
+        <v>777.59</v>
       </c>
     </row>
     <row r="952">
@@ -58539,7 +58539,7 @@
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>2050.95</v>
+        <v>2042.12</v>
       </c>
     </row>
     <row r="953">
@@ -58600,7 +58600,7 @@
         </is>
       </c>
       <c r="M953" s="2" t="n">
-        <v>1989.26</v>
+        <v>1980.69</v>
       </c>
     </row>
     <row r="954">
@@ -58661,7 +58661,7 @@
         </is>
       </c>
       <c r="M954" s="2" t="n">
-        <v>3953.45</v>
+        <v>3936.42</v>
       </c>
     </row>
     <row r="955">
@@ -58722,7 +58722,7 @@
         </is>
       </c>
       <c r="M955" s="2" t="n">
-        <v>950.08</v>
+        <v>945.99</v>
       </c>
     </row>
     <row r="956">
@@ -58783,7 +58783,7 @@
         </is>
       </c>
       <c r="M956" s="2" t="n">
-        <v>26633.28</v>
+        <v>26518.54</v>
       </c>
     </row>
     <row r="957">
@@ -58844,7 +58844,7 @@
         </is>
       </c>
       <c r="M957" s="2" t="n">
-        <v>1960.79</v>
+        <v>1952.34</v>
       </c>
     </row>
     <row r="958">
@@ -58905,7 +58905,7 @@
         </is>
       </c>
       <c r="M958" s="2" t="n">
-        <v>3009.69</v>
+        <v>2996.72</v>
       </c>
     </row>
     <row r="959">
@@ -58966,7 +58966,7 @@
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>3296.86</v>
+        <v>3282.66</v>
       </c>
     </row>
     <row r="960">
@@ -59027,7 +59027,7 @@
         </is>
       </c>
       <c r="M960" s="2" t="n">
-        <v>11007.97</v>
+        <v>10960.55</v>
       </c>
     </row>
     <row r="961">
@@ -59088,7 +59088,7 @@
         </is>
       </c>
       <c r="M961" s="2" t="n">
-        <v>2008.93</v>
+        <v>2000.27</v>
       </c>
     </row>
     <row r="962">
@@ -59149,7 +59149,7 @@
         </is>
       </c>
       <c r="M962" s="2" t="n">
-        <v>1231.4</v>
+        <v>1226.1</v>
       </c>
     </row>
     <row r="963">
@@ -59210,7 +59210,7 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>3825.55</v>
+        <v>3809.07</v>
       </c>
     </row>
     <row r="964">
@@ -59271,7 +59271,7 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>2880.36</v>
+        <v>2838.69</v>
       </c>
     </row>
     <row r="965">
@@ -59332,7 +59332,7 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>1283.99</v>
+        <v>1265.42</v>
       </c>
     </row>
     <row r="966">
@@ -59393,7 +59393,7 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>12240</v>
+        <v>12062.92</v>
       </c>
     </row>
     <row r="967">
@@ -59454,7 +59454,7 @@
         </is>
       </c>
       <c r="M967" s="2" t="n">
-        <v>4229.38</v>
+        <v>4168.19</v>
       </c>
     </row>
     <row r="968">
@@ -59515,7 +59515,7 @@
         </is>
       </c>
       <c r="M968" s="2" t="n">
-        <v>15463.82</v>
+        <v>15240.11</v>
       </c>
     </row>
     <row r="969">
@@ -59576,7 +59576,7 @@
         </is>
       </c>
       <c r="M969" s="2" t="n">
-        <v>2739.67</v>
+        <v>2700.03</v>
       </c>
     </row>
     <row r="970">
@@ -59637,7 +59637,7 @@
         </is>
       </c>
       <c r="M970" s="2" t="n">
-        <v>1219.57</v>
+        <v>1201.92</v>
       </c>
     </row>
     <row r="971">
@@ -59698,7 +59698,7 @@
         </is>
       </c>
       <c r="M971" s="2" t="n">
-        <v>1739.04</v>
+        <v>1713.88</v>
       </c>
     </row>
     <row r="972">
@@ -59759,7 +59759,7 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>2028.27</v>
+        <v>1998.93</v>
       </c>
     </row>
     <row r="973">
@@ -59820,7 +59820,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>9054.5</v>
+        <v>8923.5</v>
       </c>
     </row>
     <row r="974">
@@ -59881,7 +59881,7 @@
         </is>
       </c>
       <c r="M974" s="2" t="n">
-        <v>2274.87</v>
+        <v>2241.96</v>
       </c>
     </row>
     <row r="975">
@@ -59942,7 +59942,7 @@
         </is>
       </c>
       <c r="M975" s="2" t="n">
-        <v>1895.28</v>
+        <v>1867.86</v>
       </c>
     </row>
     <row r="976">
@@ -60003,7 +60003,7 @@
         </is>
       </c>
       <c r="M976" s="2" t="n">
-        <v>34781.37</v>
+        <v>34278.19</v>
       </c>
     </row>
     <row r="977">
@@ -60064,7 +60064,7 @@
         </is>
       </c>
       <c r="M977" s="2" t="n">
-        <v>1148.6</v>
+        <v>1131.99</v>
       </c>
     </row>
     <row r="978">
@@ -60125,7 +60125,7 @@
         </is>
       </c>
       <c r="M978" s="2" t="n">
-        <v>5117.86</v>
+        <v>5043.82</v>
       </c>
     </row>
     <row r="979">
@@ -60186,7 +60186,7 @@
         </is>
       </c>
       <c r="M979" s="2" t="n">
-        <v>17822.39</v>
+        <v>17564.55</v>
       </c>
     </row>
     <row r="980">
@@ -60247,7 +60247,7 @@
         </is>
       </c>
       <c r="M980" s="2" t="n">
-        <v>2415.98</v>
+        <v>2381.03</v>
       </c>
     </row>
     <row r="981">
@@ -60308,7 +60308,7 @@
         </is>
       </c>
       <c r="M981" s="2" t="n">
-        <v>6769.26</v>
+        <v>6671.33</v>
       </c>
     </row>
     <row r="982">
@@ -60369,7 +60369,7 @@
         </is>
       </c>
       <c r="M982" s="2" t="n">
-        <v>2322.73</v>
+        <v>2289.13</v>
       </c>
     </row>
     <row r="983">
@@ -60430,7 +60430,7 @@
         </is>
       </c>
       <c r="M983" s="2" t="n">
-        <v>7206.03</v>
+        <v>7101.78</v>
       </c>
     </row>
     <row r="984">
@@ -60491,7 +60491,7 @@
         </is>
       </c>
       <c r="M984" s="2" t="n">
-        <v>1958.17</v>
+        <v>1929.84</v>
       </c>
     </row>
     <row r="985">
@@ -60552,7 +60552,7 @@
         </is>
       </c>
       <c r="M985" s="2" t="n">
-        <v>3215.75</v>
+        <v>3169.23</v>
       </c>
     </row>
     <row r="986">
@@ -60613,7 +60613,7 @@
         </is>
       </c>
       <c r="M986" s="2" t="n">
-        <v>846.23</v>
+        <v>833.99</v>
       </c>
     </row>
     <row r="987">
@@ -60674,7 +60674,7 @@
         </is>
       </c>
       <c r="M987" s="2" t="n">
-        <v>1844.44</v>
+        <v>1817.76</v>
       </c>
     </row>
     <row r="988">
@@ -60735,7 +60735,7 @@
         </is>
       </c>
       <c r="M988" s="2" t="n">
-        <v>27380.53</v>
+        <v>26984.42</v>
       </c>
     </row>
     <row r="989">
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="M989" s="2" t="n">
-        <v>8343.73</v>
+        <v>8223.02</v>
       </c>
     </row>
     <row r="990">
@@ -60857,7 +60857,7 @@
         </is>
       </c>
       <c r="M990" s="2" t="n">
-        <v>811.1900000000001</v>
+        <v>799.46</v>
       </c>
     </row>
     <row r="991">
@@ -60918,7 +60918,7 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>2114.93</v>
+        <v>2084.33</v>
       </c>
     </row>
     <row r="992">
@@ -60979,7 +60979,7 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>1380.67</v>
+        <v>1360.69</v>
       </c>
     </row>
     <row r="993">
@@ -61040,7 +61040,7 @@
         </is>
       </c>
       <c r="M993" s="2" t="n">
-        <v>2141.25</v>
+        <v>2110.28</v>
       </c>
     </row>
     <row r="994">
@@ -61101,7 +61101,7 @@
         </is>
       </c>
       <c r="M994" s="2" t="n">
-        <v>9846.51</v>
+        <v>9704.059999999999</v>
       </c>
     </row>
     <row r="995">
@@ -61162,7 +61162,7 @@
         </is>
       </c>
       <c r="M995" s="2" t="n">
-        <v>3229.09</v>
+        <v>3182.37</v>
       </c>
     </row>
     <row r="996">
@@ -61223,7 +61223,7 @@
         </is>
       </c>
       <c r="M996" s="2" t="n">
-        <v>1128.7</v>
+        <v>1112.37</v>
       </c>
     </row>
     <row r="997">
@@ -61284,7 +61284,7 @@
         </is>
       </c>
       <c r="M997" s="2" t="n">
-        <v>12193.96</v>
+        <v>12017.55</v>
       </c>
     </row>
     <row r="998">
@@ -61345,7 +61345,7 @@
         </is>
       </c>
       <c r="M998" s="2" t="n">
-        <v>1697.82</v>
+        <v>1673.26</v>
       </c>
     </row>
     <row r="999">
@@ -61406,7 +61406,7 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>18665.58</v>
+        <v>18395.54</v>
       </c>
     </row>
     <row r="1000">
@@ -61467,7 +61467,7 @@
         </is>
       </c>
       <c r="M1000" s="2" t="n">
-        <v>5763.19</v>
+        <v>5679.82</v>
       </c>
     </row>
     <row r="1001">
@@ -61528,7 +61528,7 @@
         </is>
       </c>
       <c r="M1001" s="2" t="n">
-        <v>2666.59</v>
+        <v>2628.01</v>
       </c>
     </row>
     <row r="1002">
@@ -61589,7 +61589,7 @@
         </is>
       </c>
       <c r="M1002" s="2" t="n">
-        <v>9849.809999999999</v>
+        <v>9707.309999999999</v>
       </c>
     </row>
     <row r="1003">
@@ -61650,7 +61650,7 @@
         </is>
       </c>
       <c r="M1003" s="2" t="n">
-        <v>3776.04</v>
+        <v>3721.42</v>
       </c>
     </row>
     <row r="1004">
@@ -61711,7 +61711,7 @@
         </is>
       </c>
       <c r="M1004" s="2" t="n">
-        <v>1690.92</v>
+        <v>1666.46</v>
       </c>
     </row>
     <row r="1005">
@@ -61772,7 +61772,7 @@
         </is>
       </c>
       <c r="M1005" s="2" t="n">
-        <v>2162.56</v>
+        <v>2116.03</v>
       </c>
     </row>
     <row r="1006">
@@ -61833,7 +61833,7 @@
         </is>
       </c>
       <c r="M1006" s="2" t="n">
-        <v>2917.52</v>
+        <v>2854.75</v>
       </c>
     </row>
     <row r="1007">
@@ -61894,7 +61894,7 @@
         </is>
       </c>
       <c r="M1007" s="2" t="n">
-        <v>5569.79</v>
+        <v>5449.95</v>
       </c>
     </row>
     <row r="1008">
@@ -61955,7 +61955,7 @@
         </is>
       </c>
       <c r="M1008" s="2" t="n">
-        <v>12726.12</v>
+        <v>12452.32</v>
       </c>
     </row>
     <row r="1009">
@@ -62016,7 +62016,7 @@
         </is>
       </c>
       <c r="M1009" s="2" t="n">
-        <v>5990.31</v>
+        <v>5861.43</v>
       </c>
     </row>
     <row r="1010">
@@ -62077,7 +62077,7 @@
         </is>
       </c>
       <c r="M1010" s="2" t="n">
-        <v>6779.82</v>
+        <v>6633.95</v>
       </c>
     </row>
     <row r="1011">
@@ -62138,7 +62138,7 @@
         </is>
       </c>
       <c r="M1011" s="2" t="n">
-        <v>807.3099999999999</v>
+        <v>789.9400000000001</v>
       </c>
     </row>
     <row r="1012">
@@ -62199,7 +62199,7 @@
         </is>
       </c>
       <c r="M1012" s="2" t="n">
-        <v>13850.98</v>
+        <v>13552.97</v>
       </c>
     </row>
     <row r="1013">
@@ -62260,7 +62260,7 @@
         </is>
       </c>
       <c r="M1013" s="2" t="n">
-        <v>1061.98</v>
+        <v>1039.13</v>
       </c>
     </row>
     <row r="1014">
@@ -62321,7 +62321,7 @@
         </is>
       </c>
       <c r="M1014" s="2" t="n">
-        <v>5275.11</v>
+        <v>5161.62</v>
       </c>
     </row>
     <row r="1015">
@@ -62382,7 +62382,7 @@
         </is>
       </c>
       <c r="M1015" s="2" t="n">
-        <v>50613.63</v>
+        <v>49524.68</v>
       </c>
     </row>
     <row r="1016">
@@ -62443,7 +62443,7 @@
         </is>
       </c>
       <c r="M1016" s="2" t="n">
-        <v>2738.63</v>
+        <v>2679.71</v>
       </c>
     </row>
     <row r="1017">
@@ -62504,7 +62504,7 @@
         </is>
       </c>
       <c r="M1017" s="2" t="n">
-        <v>1520.5</v>
+        <v>1487.79</v>
       </c>
     </row>
     <row r="1018">
@@ -62565,7 +62565,7 @@
         </is>
       </c>
       <c r="M1018" s="2" t="n">
-        <v>3394.59</v>
+        <v>3321.56</v>
       </c>
     </row>
     <row r="1019">
@@ -62626,7 +62626,7 @@
         </is>
       </c>
       <c r="M1019" s="2" t="n">
-        <v>1777.21</v>
+        <v>1738.97</v>
       </c>
     </row>
     <row r="1020">
@@ -62687,7 +62687,7 @@
         </is>
       </c>
       <c r="M1020" s="2" t="n">
-        <v>2925.17</v>
+        <v>2862.23</v>
       </c>
     </row>
     <row r="1021">
@@ -62748,7 +62748,7 @@
         </is>
       </c>
       <c r="M1021" s="2" t="n">
-        <v>2016.56</v>
+        <v>1973.17</v>
       </c>
     </row>
     <row r="1022">
@@ -62809,7 +62809,7 @@
         </is>
       </c>
       <c r="M1022" s="2" t="n">
-        <v>781.16</v>
+        <v>764.35</v>
       </c>
     </row>
     <row r="1023">
@@ -62870,7 +62870,7 @@
         </is>
       </c>
       <c r="M1023" s="2" t="n">
-        <v>4531.1</v>
+        <v>4433.61</v>
       </c>
     </row>
     <row r="1024">
@@ -62931,7 +62931,7 @@
         </is>
       </c>
       <c r="M1024" s="2" t="n">
-        <v>6161.02</v>
+        <v>6028.47</v>
       </c>
     </row>
     <row r="1025">
@@ -62992,7 +62992,7 @@
         </is>
       </c>
       <c r="M1025" s="2" t="n">
-        <v>4285.49</v>
+        <v>4193.29</v>
       </c>
     </row>
     <row r="1026">
@@ -63053,7 +63053,7 @@
         </is>
       </c>
       <c r="M1026" s="2" t="n">
-        <v>2884.45</v>
+        <v>2822.39</v>
       </c>
     </row>
     <row r="1027">
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="M1027" s="2" t="n">
-        <v>5269.27</v>
+        <v>5155.91</v>
       </c>
     </row>
     <row r="1028">
@@ -63175,7 +63175,7 @@
         </is>
       </c>
       <c r="M1028" s="2" t="n">
-        <v>2468.19</v>
+        <v>2415.09</v>
       </c>
     </row>
     <row r="1029">
@@ -63236,7 +63236,7 @@
         </is>
       </c>
       <c r="M1029" s="2" t="n">
-        <v>1954.44</v>
+        <v>1912.39</v>
       </c>
     </row>
     <row r="1030">
@@ -63297,7 +63297,7 @@
         </is>
       </c>
       <c r="M1030" s="2" t="n">
-        <v>3467.94</v>
+        <v>3393.32</v>
       </c>
     </row>
     <row r="1031">
@@ -63358,7 +63358,7 @@
         </is>
       </c>
       <c r="M1031" s="2" t="n">
-        <v>1236.46</v>
+        <v>1209.86</v>
       </c>
     </row>
     <row r="1032">
@@ -63419,7 +63419,7 @@
         </is>
       </c>
       <c r="M1032" s="2" t="n">
-        <v>3553.43</v>
+        <v>3476.98</v>
       </c>
     </row>
     <row r="1033">
@@ -63480,7 +63480,7 @@
         </is>
       </c>
       <c r="M1033" s="2" t="n">
-        <v>863.01</v>
+        <v>844.4400000000001</v>
       </c>
     </row>
     <row r="1034">
@@ -63541,7 +63541,7 @@
         </is>
       </c>
       <c r="M1034" s="2" t="n">
-        <v>3647.56</v>
+        <v>3569.08</v>
       </c>
     </row>
     <row r="1035">
@@ -63602,7 +63602,7 @@
         </is>
       </c>
       <c r="M1035" s="2" t="n">
-        <v>1438.34</v>
+        <v>1407.39</v>
       </c>
     </row>
     <row r="1036">
@@ -63667,7 +63667,7 @@
         </is>
       </c>
       <c r="M1036" s="2" t="n">
-        <v>155059.83</v>
+        <v>151723.71</v>
       </c>
     </row>
     <row r="1037">
@@ -63728,7 +63728,7 @@
         </is>
       </c>
       <c r="M1037" s="2" t="n">
-        <v>3855.56</v>
+        <v>3772.61</v>
       </c>
     </row>
     <row r="1038">
@@ -63789,7 +63789,7 @@
         </is>
       </c>
       <c r="M1038" s="2" t="n">
-        <v>13289.02</v>
+        <v>13003.11</v>
       </c>
     </row>
     <row r="1039">
@@ -63850,7 +63850,7 @@
         </is>
       </c>
       <c r="M1039" s="2" t="n">
-        <v>2877.26</v>
+        <v>2815.36</v>
       </c>
     </row>
     <row r="1040">
@@ -63911,7 +63911,7 @@
         </is>
       </c>
       <c r="M1040" s="2" t="n">
-        <v>3150.38</v>
+        <v>3082.6</v>
       </c>
     </row>
     <row r="1041">
@@ -63972,7 +63972,7 @@
         </is>
       </c>
       <c r="M1041" s="2" t="n">
-        <v>1426.01</v>
+        <v>1395.33</v>
       </c>
     </row>
     <row r="1042">
@@ -64033,7 +64033,7 @@
         </is>
       </c>
       <c r="M1042" s="2" t="n">
-        <v>1511.87</v>
+        <v>1479.34</v>
       </c>
     </row>
     <row r="1043">
@@ -64094,7 +64094,7 @@
         </is>
       </c>
       <c r="M1043" s="2" t="n">
-        <v>780.8099999999999</v>
+        <v>764.01</v>
       </c>
     </row>
     <row r="1044">
@@ -64155,7 +64155,7 @@
         </is>
       </c>
       <c r="M1044" s="2" t="n">
-        <v>1045.53</v>
+        <v>1023.04</v>
       </c>
     </row>
     <row r="1045">
@@ -64216,7 +64216,7 @@
         </is>
       </c>
       <c r="M1045" s="2" t="n">
-        <v>17608.42</v>
+        <v>17229.58</v>
       </c>
     </row>
     <row r="1046">
@@ -64277,7 +64277,7 @@
         </is>
       </c>
       <c r="M1046" s="2" t="n">
-        <v>890.26</v>
+        <v>871.11</v>
       </c>
     </row>
     <row r="1047">
@@ -64338,7 +64338,7 @@
         </is>
       </c>
       <c r="M1047" s="2" t="n">
-        <v>768.27</v>
+        <v>751.74</v>
       </c>
     </row>
     <row r="1048">
@@ -64399,7 +64399,7 @@
         </is>
       </c>
       <c r="M1048" s="2" t="n">
-        <v>6016.81</v>
+        <v>5887.36</v>
       </c>
     </row>
     <row r="1049">
@@ -64460,7 +64460,7 @@
         </is>
       </c>
       <c r="M1049" s="2" t="n">
-        <v>776.96</v>
+        <v>760.24</v>
       </c>
     </row>
     <row r="1050">
@@ -64521,7 +64521,7 @@
         </is>
       </c>
       <c r="M1050" s="2" t="n">
-        <v>8258.75</v>
+        <v>8081.07</v>
       </c>
     </row>
     <row r="1051">
@@ -64582,7 +64582,7 @@
         </is>
       </c>
       <c r="M1051" s="2" t="n">
-        <v>1487.98</v>
+        <v>1455.96</v>
       </c>
     </row>
     <row r="1052">
@@ -64643,7 +64643,7 @@
         </is>
       </c>
       <c r="M1052" s="2" t="n">
-        <v>5061.38</v>
+        <v>4952.49</v>
       </c>
     </row>
     <row r="1053">
@@ -64704,7 +64704,7 @@
         </is>
       </c>
       <c r="M1053" s="2" t="n">
-        <v>12751.5</v>
+        <v>12454.78</v>
       </c>
     </row>
     <row r="1054">
@@ -64765,7 +64765,7 @@
         </is>
       </c>
       <c r="M1054" s="2" t="n">
-        <v>1424.37</v>
+        <v>1391.22</v>
       </c>
     </row>
     <row r="1055">
@@ -64826,7 +64826,7 @@
         </is>
       </c>
       <c r="M1055" s="2" t="n">
-        <v>19164</v>
+        <v>18718.07</v>
       </c>
     </row>
     <row r="1056">
@@ -64887,7 +64887,7 @@
         </is>
       </c>
       <c r="M1056" s="2" t="n">
-        <v>2695.93</v>
+        <v>2633.19</v>
       </c>
     </row>
     <row r="1057">
@@ -64948,7 +64948,7 @@
         </is>
       </c>
       <c r="M1057" s="2" t="n">
-        <v>2082.93</v>
+        <v>2034.46</v>
       </c>
     </row>
     <row r="1058">
@@ -65009,7 +65009,7 @@
         </is>
       </c>
       <c r="M1058" s="2" t="n">
-        <v>4253.79</v>
+        <v>4154.81</v>
       </c>
     </row>
     <row r="1059">
@@ -65070,7 +65070,7 @@
         </is>
       </c>
       <c r="M1059" s="2" t="n">
-        <v>7587.87</v>
+        <v>7411.31</v>
       </c>
     </row>
     <row r="1060">
@@ -65131,7 +65131,7 @@
         </is>
       </c>
       <c r="M1060" s="2" t="n">
-        <v>3250</v>
+        <v>3174.37</v>
       </c>
     </row>
     <row r="1061">
@@ -65192,7 +65192,7 @@
         </is>
       </c>
       <c r="M1061" s="2" t="n">
-        <v>7553.59</v>
+        <v>7377.83</v>
       </c>
     </row>
     <row r="1062">
@@ -65253,7 +65253,7 @@
         </is>
       </c>
       <c r="M1062" s="2" t="n">
-        <v>2024.87</v>
+        <v>1977.75</v>
       </c>
     </row>
     <row r="1063">
@@ -65314,7 +65314,7 @@
         </is>
       </c>
       <c r="M1063" s="2" t="n">
-        <v>4763.17</v>
+        <v>4652.34</v>
       </c>
     </row>
     <row r="1064">
@@ -65375,7 +65375,7 @@
         </is>
       </c>
       <c r="M1064" s="2" t="n">
-        <v>1578.93</v>
+        <v>1542.19</v>
       </c>
     </row>
     <row r="1065">
@@ -65436,7 +65436,7 @@
         </is>
       </c>
       <c r="M1065" s="2" t="n">
-        <v>3977</v>
+        <v>3884.46</v>
       </c>
     </row>
     <row r="1066">
@@ -65497,7 +65497,7 @@
         </is>
       </c>
       <c r="M1066" s="2" t="n">
-        <v>2559.65</v>
+        <v>2500.09</v>
       </c>
     </row>
     <row r="1067">
@@ -65558,7 +65558,7 @@
         </is>
       </c>
       <c r="M1067" s="2" t="n">
-        <v>2851.08</v>
+        <v>2784.74</v>
       </c>
     </row>
     <row r="1068">
@@ -65619,7 +65619,7 @@
         </is>
       </c>
       <c r="M1068" s="2" t="n">
-        <v>18226.88</v>
+        <v>17802.76</v>
       </c>
     </row>
     <row r="1069">
@@ -65680,7 +65680,7 @@
         </is>
       </c>
       <c r="M1069" s="2" t="n">
-        <v>5149.43</v>
+        <v>5029.61</v>
       </c>
     </row>
     <row r="1070">
@@ -65741,7 +65741,7 @@
         </is>
       </c>
       <c r="M1070" s="2" t="n">
-        <v>3593.25</v>
+        <v>3509.64</v>
       </c>
     </row>
     <row r="1071">
@@ -65802,7 +65802,7 @@
         </is>
       </c>
       <c r="M1071" s="2" t="n">
-        <v>982.3</v>
+        <v>959.4400000000001</v>
       </c>
     </row>
     <row r="1072">
@@ -65863,7 +65863,7 @@
         </is>
       </c>
       <c r="M1072" s="2" t="n">
-        <v>38847.94</v>
+        <v>37943.98</v>
       </c>
     </row>
     <row r="1073">
@@ -65924,7 +65924,7 @@
         </is>
       </c>
       <c r="M1073" s="2" t="n">
-        <v>783.4</v>
+        <v>765.17</v>
       </c>
     </row>
     <row r="1074">
@@ -65985,7 +65985,7 @@
         </is>
       </c>
       <c r="M1074" s="2" t="n">
-        <v>45864.73</v>
+        <v>44797.5</v>
       </c>
     </row>
     <row r="1075">
@@ -66046,7 +66046,7 @@
         </is>
       </c>
       <c r="M1075" s="2" t="n">
-        <v>2625.91</v>
+        <v>2564.81</v>
       </c>
     </row>
     <row r="1076">
@@ -66107,7 +66107,7 @@
         </is>
       </c>
       <c r="M1076" s="2" t="n">
-        <v>11087.53</v>
+        <v>10829.53</v>
       </c>
     </row>
     <row r="1077">
@@ -66168,7 +66168,7 @@
         </is>
       </c>
       <c r="M1077" s="2" t="n">
-        <v>2725.24</v>
+        <v>2661.83</v>
       </c>
     </row>
     <row r="1078">
@@ -66229,7 +66229,7 @@
         </is>
       </c>
       <c r="M1078" s="2" t="n">
-        <v>933.64</v>
+        <v>911.92</v>
       </c>
     </row>
     <row r="1079">
@@ -66290,7 +66290,7 @@
         </is>
       </c>
       <c r="M1079" s="2" t="n">
-        <v>14511.56</v>
+        <v>14173.89</v>
       </c>
     </row>
     <row r="1080">
@@ -66351,7 +66351,7 @@
         </is>
       </c>
       <c r="M1080" s="2" t="n">
-        <v>3434.18</v>
+        <v>3354.27</v>
       </c>
     </row>
     <row r="1081">
@@ -66412,7 +66412,7 @@
         </is>
       </c>
       <c r="M1081" s="2" t="n">
-        <v>11709.21</v>
+        <v>11436.75</v>
       </c>
     </row>
     <row r="1082">
@@ -66473,7 +66473,7 @@
         </is>
       </c>
       <c r="M1082" s="2" t="n">
-        <v>3394.36</v>
+        <v>3315.38</v>
       </c>
     </row>
     <row r="1083">
@@ -66534,7 +66534,7 @@
         </is>
       </c>
       <c r="M1083" s="2" t="n">
-        <v>874.97</v>
+        <v>854.61</v>
       </c>
     </row>
     <row r="1084">
@@ -66595,7 +66595,7 @@
         </is>
       </c>
       <c r="M1084" s="2" t="n">
-        <v>11364.05</v>
+        <v>11099.62</v>
       </c>
     </row>
     <row r="1085">
@@ -66656,7 +66656,7 @@
         </is>
       </c>
       <c r="M1085" s="2" t="n">
-        <v>33754.45</v>
+        <v>32969.02</v>
       </c>
     </row>
     <row r="1086">
@@ -66717,7 +66717,7 @@
         </is>
       </c>
       <c r="M1086" s="2" t="n">
-        <v>2937.34</v>
+        <v>2868.99</v>
       </c>
     </row>
     <row r="1087">
@@ -66778,7 +66778,7 @@
         </is>
       </c>
       <c r="M1087" s="2" t="n">
-        <v>1098.44</v>
+        <v>1072.88</v>
       </c>
     </row>
     <row r="1088">
@@ -66839,7 +66839,7 @@
         </is>
       </c>
       <c r="M1088" s="2" t="n">
-        <v>1155.35</v>
+        <v>1128.47</v>
       </c>
     </row>
     <row r="1089">
@@ -66900,7 +66900,7 @@
         </is>
       </c>
       <c r="M1089" s="2" t="n">
-        <v>10761.44</v>
+        <v>10511.03</v>
       </c>
     </row>
     <row r="1090">
@@ -66961,7 +66961,7 @@
         </is>
       </c>
       <c r="M1090" s="2" t="n">
-        <v>1101.21</v>
+        <v>1075.58</v>
       </c>
     </row>
     <row r="1091">
@@ -67022,7 +67022,7 @@
         </is>
       </c>
       <c r="M1091" s="2" t="n">
-        <v>25790.81</v>
+        <v>25190.68</v>
       </c>
     </row>
     <row r="1092">
@@ -67083,7 +67083,7 @@
         </is>
       </c>
       <c r="M1092" s="2" t="n">
-        <v>2946.03</v>
+        <v>2877.47</v>
       </c>
     </row>
     <row r="1093">
@@ -67144,7 +67144,7 @@
         </is>
       </c>
       <c r="M1093" s="2" t="n">
-        <v>960.51</v>
+        <v>938.16</v>
       </c>
     </row>
     <row r="1094">
@@ -67205,7 +67205,7 @@
         </is>
       </c>
       <c r="M1094" s="2" t="n">
-        <v>4392.01</v>
+        <v>4289.81</v>
       </c>
     </row>
     <row r="1095">
@@ -67266,7 +67266,7 @@
         </is>
       </c>
       <c r="M1095" s="2" t="n">
-        <v>1636.65</v>
+        <v>1598.56</v>
       </c>
     </row>
     <row r="1096">
@@ -67327,7 +67327,7 @@
         </is>
       </c>
       <c r="M1096" s="2" t="n">
-        <v>770.02</v>
+        <v>752.11</v>
       </c>
     </row>
     <row r="1097">
@@ -67388,7 +67388,7 @@
         </is>
       </c>
       <c r="M1097" s="2" t="n">
-        <v>16458.87</v>
+        <v>16075.88</v>
       </c>
     </row>
     <row r="1098">
@@ -67449,7 +67449,7 @@
         </is>
       </c>
       <c r="M1098" s="2" t="n">
-        <v>1151.95</v>
+        <v>1125.15</v>
       </c>
     </row>
     <row r="1099">
@@ -67510,7 +67510,7 @@
         </is>
       </c>
       <c r="M1099" s="2" t="n">
-        <v>18080.71</v>
+        <v>17659.98</v>
       </c>
     </row>
     <row r="1100">
@@ -67571,7 +67571,7 @@
         </is>
       </c>
       <c r="M1100" s="2" t="n">
-        <v>991.4400000000001</v>
+        <v>968.37</v>
       </c>
     </row>
     <row r="1101">
@@ -67632,7 +67632,7 @@
         </is>
       </c>
       <c r="M1101" s="2" t="n">
-        <v>1498.69</v>
+        <v>1463.82</v>
       </c>
     </row>
     <row r="1102">
@@ -67693,7 +67693,7 @@
         </is>
       </c>
       <c r="M1102" s="2" t="n">
-        <v>809.9400000000001</v>
+        <v>791.09</v>
       </c>
     </row>
     <row r="1103">
@@ -67754,7 +67754,7 @@
         </is>
       </c>
       <c r="M1103" s="2" t="n">
-        <v>1592.92</v>
+        <v>1555.86</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20447,7 +20447,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23253,7 +23253,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -27039,7 +27039,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27405,7 +27405,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27710,7 +27710,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -28503,7 +28503,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -29845,7 +29845,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30089,7 +30089,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30272,7 +30272,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30577,7 +30577,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30760,7 +30760,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31431,7 +31431,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31919,7 +31919,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32346,7 +32346,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32895,7 +32895,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33444,7 +33444,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33810,7 +33810,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33932,7 +33932,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -34603,7 +34603,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34786,7 +34786,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34847,7 +34847,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -35213,7 +35213,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35701,7 +35701,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35762,7 +35762,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -38690,7 +38690,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38812,7 +38812,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -39178,7 +39178,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39376,7 +39376,7 @@
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
@@ -39487,7 +39487,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39548,7 +39548,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -41378,7 +41378,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -43025,7 +43025,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43635,7 +43635,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43696,7 +43696,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43879,7 +43879,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44489,7 +44489,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44672,7 +44672,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -45160,7 +45160,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45221,7 +45221,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45282,7 +45282,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45770,7 +45770,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45953,7 +45953,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46014,7 +46014,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46258,7 +46258,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46746,7 +46746,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -47295,7 +47295,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47478,7 +47478,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -48027,7 +48027,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48210,7 +48210,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -48698,7 +48698,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48942,7 +48942,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -49369,7 +49369,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -49796,7 +49796,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -49918,7 +49918,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -50284,7 +50284,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -50406,7 +50406,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -50467,7 +50467,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -50772,7 +50772,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -50833,7 +50833,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -50894,7 +50894,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -52053,7 +52053,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -52175,7 +52175,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -52236,7 +52236,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -52297,7 +52297,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -52419,7 +52419,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -53151,7 +53151,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
@@ -53273,7 +53273,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53944,7 +53944,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -54798,7 +54798,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -54981,7 +54981,7 @@
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -55591,7 +55591,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -56445,7 +56445,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -56750,7 +56750,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -58519,7 +58519,7 @@
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
@@ -58702,7 +58702,7 @@
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
@@ -58946,7 +58946,7 @@
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -59007,7 +59007,7 @@
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
@@ -59312,7 +59312,7 @@
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -59556,7 +59556,7 @@
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
@@ -60044,7 +60044,7 @@
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
@@ -60471,7 +60471,7 @@
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -60837,7 +60837,7 @@
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
@@ -60898,7 +60898,7 @@
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
@@ -61386,7 +61386,7 @@
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -61569,7 +61569,7 @@
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -61996,7 +61996,7 @@
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
@@ -62118,7 +62118,7 @@
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
@@ -62179,7 +62179,7 @@
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -62240,7 +62240,7 @@
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
@@ -62301,7 +62301,7 @@
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -63094,7 +63094,7 @@
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
@@ -63658,7 +63658,7 @@
       </c>
       <c r="K1036" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1036" t="inlineStr">
@@ -64379,7 +64379,7 @@
       </c>
       <c r="H1048" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1048" t="inlineStr">
@@ -64562,7 +64562,7 @@
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
@@ -65233,7 +65233,7 @@
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
@@ -66331,7 +66331,7 @@
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
@@ -66819,7 +66819,7 @@
       </c>
       <c r="H1088" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1088" t="inlineStr">
@@ -66880,7 +66880,7 @@
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
@@ -66941,7 +66941,7 @@
       </c>
       <c r="H1090" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1090" t="inlineStr">
@@ -67002,7 +67002,7 @@
       </c>
       <c r="H1091" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
@@ -67124,7 +67124,7 @@
       </c>
       <c r="H1093" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
@@ -67612,7 +67612,7 @@
       </c>
       <c r="H1101" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1101" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cochamó - Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación San Antonio</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>MUSEO NACIONAL DE BELLAS ARTES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12748,12 +12748,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18612,7 +18612,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Economato C.C.P. Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Brigada de Inteligencia del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Brigada de Inteligencia del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -19832,7 +19832,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -20259,12 +20259,12 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21540,12 +21540,12 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22943,7 +22943,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23253,12 +23253,12 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región Metropiltana de Santiago</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Economato</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25027,7 +25027,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -25458,7 +25458,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>IMPO PAPER SPA</t>
+          <t>Impo Paper Spa</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -26058,7 +26058,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -26617,7 +26617,7 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>IMPO PAPER SPA</t>
+          <t>Impo Paper Spa</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -27217,7 +27217,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27227,7 +27227,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -27522,12 +27522,12 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -28503,7 +28503,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28559,7 +28559,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -28803,7 +28803,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -28925,7 +28925,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -28986,7 +28986,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29657,7 +29657,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29718,7 +29718,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30094,7 +30094,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -30277,7 +30277,7 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -30389,7 +30389,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>MINEDUC ADMINISTRACION VIII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
@@ -30455,7 +30455,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -30694,7 +30694,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -30755,7 +30755,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -31065,12 +31065,12 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -31548,7 +31548,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31558,7 +31558,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -31670,7 +31670,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -31965,7 +31965,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32412,7 +32412,7 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
@@ -32595,7 +32595,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -32646,7 +32646,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32900,7 +32900,7 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
@@ -32951,7 +32951,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -33205,7 +33205,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
@@ -34303,7 +34303,7 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -34842,7 +34842,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -35035,7 +35035,7 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -35269,17 +35269,17 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial Región  Biobío</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -35818,7 +35818,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial Región  Biobío</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -35889,7 +35889,7 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Contraloría de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -36133,7 +36133,7 @@
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J585" t="inlineStr">
@@ -36194,7 +36194,7 @@
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J586" t="inlineStr">
@@ -36245,7 +36245,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
@@ -36672,7 +36672,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -36743,7 +36743,7 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
@@ -37099,7 +37099,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -37597,7 +37597,7 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
@@ -37648,7 +37648,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -37780,7 +37780,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38695,7 +38695,7 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
@@ -38746,7 +38746,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -38817,7 +38817,7 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
@@ -38868,7 +38868,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -38878,7 +38878,7 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Centro de Perfeccionamiento, Experimentación e Inv</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -39112,7 +39112,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39122,7 +39122,7 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -39482,7 +39482,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -39604,7 +39604,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -39614,7 +39614,7 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
@@ -39909,7 +39909,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -40031,7 +40031,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -40092,7 +40092,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -40163,7 +40163,7 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
@@ -40214,7 +40214,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -40397,7 +40397,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -40407,7 +40407,7 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
@@ -40519,7 +40519,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -40702,7 +40702,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -40885,7 +40885,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -40956,7 +40956,7 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
@@ -41251,7 +41251,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -41373,7 +41373,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -41434,7 +41434,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -41444,7 +41444,7 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
@@ -41566,7 +41566,7 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -41617,7 +41617,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41678,7 +41678,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -41739,7 +41739,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -41927,7 +41927,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41983,7 +41983,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -41993,7 +41993,7 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -42176,7 +42176,7 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
@@ -42471,7 +42471,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -42654,17 +42654,17 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
@@ -42715,12 +42715,12 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -42959,7 +42959,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -42969,7 +42969,7 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
@@ -43020,7 +43020,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -43640,7 +43640,7 @@
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -43823,7 +43823,7 @@
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
@@ -43884,7 +43884,7 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
@@ -44057,7 +44057,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44067,7 +44067,7 @@
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
@@ -44118,7 +44118,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -44240,7 +44240,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -44667,7 +44667,7 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Gendarmeria de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -44728,7 +44728,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -44789,7 +44789,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -44860,7 +44860,7 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
@@ -44921,7 +44921,7 @@
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
@@ -45104,7 +45104,7 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO ANDRES </t>
+          <t xml:space="preserve">Eduardo Andres </t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
@@ -45216,7 +45216,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -45338,7 +45338,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -45399,7 +45399,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -45460,7 +45460,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -45582,7 +45582,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -45765,7 +45765,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -45887,7 +45887,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Curacautín</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -45897,7 +45897,7 @@
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
@@ -45948,7 +45948,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -46507,7 +46507,7 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVET SPA </t>
+          <t>LIVET SPA</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
@@ -46680,7 +46680,7 @@
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -46863,7 +46863,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -47229,7 +47229,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -47412,7 +47412,7 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -47473,7 +47473,7 @@
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -47534,7 +47534,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -47544,7 +47544,7 @@
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
@@ -47605,7 +47605,7 @@
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
@@ -47656,7 +47656,7 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -47666,7 +47666,7 @@
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>INGESCOM LTDA.</t>
+          <t>Ingescom ltda.</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -47717,7 +47717,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -47727,7 +47727,7 @@
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -47788,7 +47788,7 @@
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
@@ -47910,7 +47910,7 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -47971,7 +47971,7 @@
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
@@ -48093,7 +48093,7 @@
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO ANDRES </t>
+          <t xml:space="preserve">Eduardo Andres </t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
@@ -48144,7 +48144,7 @@
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>Dirección General de Gendarmería de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -48205,7 +48205,7 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -48337,7 +48337,7 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -48754,7 +48754,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. de la División Logística</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -48886,7 +48886,7 @@
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -48998,12 +48998,12 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -49496,7 +49496,7 @@
       </c>
       <c r="I804" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J804" t="inlineStr">
@@ -49669,7 +49669,7 @@
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
@@ -49984,7 +49984,7 @@
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
@@ -50167,7 +50167,7 @@
       </c>
       <c r="I815" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J815" t="inlineStr">
@@ -50218,7 +50218,7 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -50401,7 +50401,7 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
@@ -50523,7 +50523,7 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
@@ -50960,7 +50960,7 @@
       </c>
       <c r="I828" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J828" t="inlineStr">
@@ -51011,7 +51011,7 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
@@ -51021,7 +51021,7 @@
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
@@ -51072,7 +51072,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -51133,7 +51133,7 @@
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
@@ -51194,7 +51194,7 @@
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
@@ -51255,7 +51255,7 @@
       </c>
       <c r="G833" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H833" t="inlineStr">
@@ -51316,7 +51316,7 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
@@ -51499,7 +51499,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Feria Internacional del Aire y del Espacio</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -51865,7 +51865,7 @@
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
@@ -51997,7 +51997,7 @@
       </c>
       <c r="I845" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO ANDRES </t>
+          <t xml:space="preserve">Eduardo Andres </t>
         </is>
       </c>
       <c r="J845" t="inlineStr">
@@ -52414,7 +52414,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -52658,7 +52658,7 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
@@ -52841,7 +52841,7 @@
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
@@ -52902,7 +52902,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H862" t="inlineStr">
@@ -53146,7 +53146,7 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
@@ -53156,7 +53156,7 @@
       </c>
       <c r="I864" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J864" t="inlineStr">
@@ -53278,7 +53278,7 @@
       </c>
       <c r="I866" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J866" t="inlineStr">
@@ -53451,7 +53451,7 @@
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -53461,7 +53461,7 @@
       </c>
       <c r="I869" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J869" t="inlineStr">
@@ -53766,7 +53766,7 @@
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J874" t="inlineStr">
@@ -53817,7 +53817,7 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -53888,7 +53888,7 @@
       </c>
       <c r="I876" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J876" t="inlineStr">
@@ -53939,7 +53939,7 @@
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
@@ -54000,7 +54000,7 @@
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
@@ -54071,7 +54071,7 @@
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J879" t="inlineStr">
@@ -54132,7 +54132,7 @@
       </c>
       <c r="I880" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J880" t="inlineStr">
@@ -54193,7 +54193,7 @@
       </c>
       <c r="I881" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIAL MIR Y CRUZ SPA</t>
+          <t>IMPORTADORA Y COMERCIAL MIR Y CRUZ SpA</t>
         </is>
       </c>
       <c r="J881" t="inlineStr">
@@ -54244,7 +54244,7 @@
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
@@ -54305,7 +54305,7 @@
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -54315,7 +54315,7 @@
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J883" t="inlineStr">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
@@ -54427,7 +54427,7 @@
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -54793,7 +54793,7 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
@@ -54915,7 +54915,7 @@
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
@@ -54986,7 +54986,7 @@
       </c>
       <c r="I894" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J894" t="inlineStr">
@@ -55047,7 +55047,7 @@
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J895" t="inlineStr">
@@ -55108,7 +55108,7 @@
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J896" t="inlineStr">
@@ -55220,7 +55220,7 @@
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERPLAC VII REGION								</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -55342,7 +55342,7 @@
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -55535,7 +55535,7 @@
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVET SPA </t>
+          <t>LIVET SPA</t>
         </is>
       </c>
       <c r="J903" t="inlineStr">
@@ -55718,7 +55718,7 @@
       </c>
       <c r="I906" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J906" t="inlineStr">
@@ -55891,7 +55891,7 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
@@ -56023,7 +56023,7 @@
       </c>
       <c r="I911" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J911" t="inlineStr">
@@ -56328,7 +56328,7 @@
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>Said Mauricio Tarzijan Julian</t>
+          <t>SAID MAURICIO TARZIJAN JULIAN</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
@@ -56389,7 +56389,7 @@
       </c>
       <c r="I917" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J917" t="inlineStr">
@@ -56623,7 +56623,7 @@
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
@@ -56633,7 +56633,7 @@
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
@@ -56694,7 +56694,7 @@
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
@@ -56745,7 +56745,7 @@
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>ILUSTRE MUJNICIPALIDAD DE CAÑETE</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
@@ -56999,7 +56999,7 @@
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J927" t="inlineStr">
@@ -57050,7 +57050,7 @@
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
@@ -57111,7 +57111,7 @@
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
@@ -57294,7 +57294,7 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -57477,7 +57477,7 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -57660,7 +57660,7 @@
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
@@ -57670,7 +57670,7 @@
       </c>
       <c r="I938" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J938" t="inlineStr">
@@ -58087,7 +58087,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -58209,7 +58209,7 @@
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>Economato Centro Cumplimiento Penitenciario Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
@@ -58270,7 +58270,7 @@
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>Economato Centro Cumplimiento Penitenciario Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
@@ -58331,7 +58331,7 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
@@ -58768,7 +58768,7 @@
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J956" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="I959" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J959" t="inlineStr">
@@ -59002,7 +59002,7 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>Departamento de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
@@ -59063,7 +59063,7 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>2° Juzgado de Letras del Trabajo de Santiago</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H961" t="inlineStr">
@@ -59185,7 +59185,7 @@
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
@@ -59256,7 +59256,7 @@
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
@@ -59307,7 +59307,7 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -59368,7 +59368,7 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
@@ -59622,7 +59622,7 @@
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
@@ -59988,7 +59988,7 @@
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J976" t="inlineStr">
@@ -60049,7 +60049,7 @@
       </c>
       <c r="I977" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J977" t="inlineStr">
@@ -60212,7 +60212,7 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
@@ -60232,7 +60232,7 @@
       </c>
       <c r="I980" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J980" t="inlineStr">
@@ -60598,7 +60598,7 @@
       </c>
       <c r="I986" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J986" t="inlineStr">
@@ -60771,17 +60771,17 @@
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J989" t="inlineStr">
@@ -60837,7 +60837,7 @@
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
@@ -60893,7 +60893,7 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
@@ -61015,7 +61015,7 @@
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
@@ -61086,7 +61086,7 @@
       </c>
       <c r="I994" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J994" t="inlineStr">
@@ -61696,7 +61696,7 @@
       </c>
       <c r="I1004" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1004" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1005" t="inlineStr">
@@ -61879,7 +61879,7 @@
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1007" t="inlineStr">
@@ -62113,7 +62113,7 @@
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
@@ -62296,7 +62296,7 @@
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H1014" t="inlineStr">
@@ -62357,7 +62357,7 @@
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
@@ -62611,7 +62611,7 @@
       </c>
       <c r="I1019" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1019" t="inlineStr">
@@ -62662,7 +62662,7 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>Economato C.C.P. Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
@@ -62672,7 +62672,7 @@
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1020" t="inlineStr">
@@ -62784,7 +62784,7 @@
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -62906,7 +62906,7 @@
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
@@ -62916,7 +62916,7 @@
       </c>
       <c r="I1024" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1024" t="inlineStr">
@@ -63160,7 +63160,7 @@
       </c>
       <c r="I1028" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J1028" t="inlineStr">
@@ -63455,7 +63455,7 @@
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
@@ -63465,7 +63465,7 @@
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
@@ -63577,7 +63577,7 @@
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
@@ -63587,7 +63587,7 @@
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1035" t="inlineStr">
@@ -63703,7 +63703,7 @@
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
@@ -64008,7 +64008,7 @@
       </c>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr">
@@ -64252,7 +64252,7 @@
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
@@ -64313,7 +64313,7 @@
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H1047" t="inlineStr">
@@ -64435,7 +64435,7 @@
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
@@ -64679,7 +64679,7 @@
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
@@ -64801,7 +64801,7 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
@@ -64867,7 +64867,7 @@
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
@@ -64923,7 +64923,7 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
@@ -64984,7 +64984,7 @@
       </c>
       <c r="G1058" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
@@ -65177,7 +65177,7 @@
       </c>
       <c r="I1061" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1061" t="inlineStr">
@@ -65289,7 +65289,7 @@
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H1063" t="inlineStr">
@@ -65604,7 +65604,7 @@
       </c>
       <c r="I1068" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J1068" t="inlineStr">
@@ -65777,7 +65777,7 @@
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H1071" t="inlineStr">
@@ -65838,7 +65838,7 @@
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
@@ -65848,7 +65848,7 @@
       </c>
       <c r="I1072" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1072" t="inlineStr">
@@ -65909,7 +65909,7 @@
       </c>
       <c r="I1073" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1073" t="inlineStr">
@@ -66143,7 +66143,7 @@
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr">
@@ -66153,7 +66153,7 @@
       </c>
       <c r="I1077" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1077" t="inlineStr">
@@ -66204,7 +66204,7 @@
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr">
@@ -66326,7 +66326,7 @@
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr">
@@ -66397,7 +66397,7 @@
       </c>
       <c r="I1081" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1081" t="inlineStr">
@@ -66519,7 +66519,7 @@
       </c>
       <c r="I1083" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1083" t="inlineStr">
@@ -66763,7 +66763,7 @@
       </c>
       <c r="I1087" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1087" t="inlineStr">
@@ -66814,7 +66814,7 @@
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H1088" t="inlineStr">
@@ -66875,7 +66875,7 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr">
@@ -66936,7 +66936,7 @@
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H1090" t="inlineStr">
@@ -66997,7 +66997,7 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
@@ -67180,7 +67180,7 @@
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr">
@@ -67241,7 +67241,7 @@
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr">
@@ -67302,7 +67302,7 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>Juzgado de Letras y Garantía de Pucón</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1096" t="inlineStr">
@@ -67373,7 +67373,7 @@
       </c>
       <c r="I1097" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J1097" t="inlineStr">
@@ -67490,7 +67490,7 @@
       </c>
       <c r="H1099" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I1099" t="inlineStr">
@@ -67546,7 +67546,7 @@
       </c>
       <c r="G1100" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1100" t="inlineStr">
@@ -67556,7 +67556,7 @@
       </c>
       <c r="I1100" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J1100" t="inlineStr">
@@ -67668,12 +67668,12 @@
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H1102" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I1102" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
@@ -623,7 +623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2155,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2529,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2781,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2911,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3037,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3163,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3228,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3354,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3419,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3484,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3549,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3740,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3927,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3992,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4122,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4187,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4313,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4378,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4443,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4508,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4573,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4821,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4947,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5012,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5077,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5142,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5207,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5272,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5467,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5658,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5910,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6101,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6166,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6231,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6296,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6361,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6548,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6678,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6743,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6808,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6873,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6999,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7125,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7499,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7877,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8003,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8194,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8446,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8511,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8576,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8702,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8767,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8832,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8897,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8962,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9027,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9092,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9157,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9222,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9348,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9413,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9478,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9543,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9608,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9673,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9860,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9925,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9990,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10116,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10181,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10246,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10372,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10559,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10685,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10811,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10876,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11002,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11067,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11132,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11197,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11262,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11457,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11522,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11652,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11778,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11843,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11908,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12034,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12099,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12164,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12229,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12355,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12481,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12546,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12611,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12737,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12863,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12993,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13058,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13184,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13249,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13314,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13379,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13444,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13509,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13574,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13639,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13704,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13769,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13834,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13899,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13964,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13502,7 +14094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +14159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13685,7 +14285,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14350,11 @@
           <t>76.715.074-1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13807,7 +14415,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13868,7 +14480,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14545,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14051,7 +14671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14736,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14234,7 +14862,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14539,7 +15171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15419,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15484,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14905,7 +15549,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15088,7 +15736,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15801,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15210,7 +15866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15271,7 +15931,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +16057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +16122,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16435,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15820,7 +16500,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16565,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15942,7 +16630,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16125,7 +16817,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16247,7 +16943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +17008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +17073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17260,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16613,7 +17325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17455,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17581,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +17707,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +17833,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +17898,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18024,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18150,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18398,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18524,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18589,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18715,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18081,7 +18845,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18203,7 +18971,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18386,7 +19158,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18508,7 +19284,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18569,7 +19349,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18691,7 +19475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18813,7 +19601,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18874,7 +19666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18935,7 +19731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19240,7 +20040,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19301,7 +20105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19362,7 +20170,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19484,7 +20296,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19545,7 +20361,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19667,7 +20487,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19789,7 +20613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19850,7 +20678,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19911,7 +20743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19972,7 +20808,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20033,7 +20873,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20094,7 +20938,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20216,7 +21064,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20338,7 +21190,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20399,7 +21255,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20460,7 +21320,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20582,7 +21446,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20643,7 +21511,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20704,7 +21576,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20765,7 +21641,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20887,7 +21767,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20948,7 +21832,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21009,7 +21897,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21070,7 +21962,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21131,7 +22027,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21192,7 +22092,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21253,7 +22157,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21314,7 +22222,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21375,7 +22287,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21436,7 +22352,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21497,7 +22417,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21680,7 +22604,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21741,7 +22669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21802,7 +22734,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21863,7 +22799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21924,7 +22864,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21985,7 +22929,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22107,7 +23055,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22168,7 +23120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22229,7 +23185,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22290,7 +23250,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22412,7 +23376,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22473,7 +23441,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22595,7 +23567,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22656,7 +23632,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22717,7 +23697,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22778,7 +23762,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22839,7 +23827,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22900,7 +23892,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22961,7 +23957,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23022,7 +24022,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23083,7 +24087,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23327,7 +24335,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23388,7 +24400,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23449,7 +24465,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23632,7 +24652,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23754,7 +24778,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23815,7 +24843,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23876,7 +24908,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23937,7 +24973,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23998,7 +25038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24059,7 +25103,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24120,7 +25168,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24181,7 +25233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24242,7 +25298,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24303,7 +25363,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24364,7 +25428,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24425,7 +25493,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24486,7 +25558,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24608,7 +25684,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24669,7 +25749,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24730,7 +25814,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24791,7 +25879,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24852,7 +25944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24974,7 +26070,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25096,7 +26196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25222,7 +26326,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25344,7 +26452,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25527,7 +26639,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25588,7 +26704,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25649,7 +26769,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25710,7 +26834,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26076,7 +27204,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26137,7 +27269,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26198,7 +27334,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26320,7 +27460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26381,7 +27525,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26503,7 +27651,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26564,7 +27716,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26686,7 +27842,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26808,7 +27968,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26991,7 +28155,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27052,7 +28220,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27113,7 +28285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27174,7 +28350,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27296,7 +28476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27418,7 +28602,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27479,7 +28667,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27540,7 +28732,11 @@
           <t>78.201.425-0</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27662,7 +28858,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27723,7 +28923,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27845,7 +29049,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27906,7 +29114,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27967,7 +29179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28089,7 +29305,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28150,7 +29370,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28272,7 +29496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28333,7 +29561,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28394,7 +29626,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28516,7 +29752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28577,7 +29817,11 @@
           <t>76.715.074-1</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28638,7 +29882,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28699,7 +29947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28760,7 +30012,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28882,7 +30138,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28943,7 +30203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29004,7 +30268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29126,7 +30394,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29187,7 +30459,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29248,7 +30524,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29309,7 +30589,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29370,7 +30654,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29492,7 +30780,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29553,7 +30845,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29614,7 +30910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29675,7 +30975,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29736,7 +31040,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29919,7 +31227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30041,7 +31353,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30163,7 +31479,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30346,7 +31666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30468,7 +31792,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30651,7 +31979,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30712,7 +32044,11 @@
           <t>77.037.031-0</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30834,7 +32170,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30895,7 +32235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31139,7 +32483,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31200,7 +32548,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31261,7 +32613,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31322,7 +32678,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31444,7 +32804,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31627,7 +32991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31810,7 +33178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31871,7 +33243,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31932,7 +33308,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31993,7 +33373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32054,7 +33438,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32115,7 +33503,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32237,7 +33629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32298,7 +33694,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32359,7 +33759,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32481,7 +33885,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32542,7 +33950,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32664,7 +34076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32725,7 +34141,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32786,7 +34206,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32847,7 +34271,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32969,7 +34397,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33030,7 +34462,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33091,7 +34527,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33152,7 +34592,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33213,7 +34657,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33274,7 +34722,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33335,7 +34787,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33396,7 +34852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33457,7 +34917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33518,7 +34982,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33640,7 +35108,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33701,7 +35173,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34067,7 +35543,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34372,7 +35852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34433,7 +35917,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34494,7 +35982,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34555,7 +36047,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34616,7 +36112,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34677,7 +36177,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34799,7 +36303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34982,7 +36490,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35104,7 +36616,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35165,7 +36681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35226,7 +36746,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35348,7 +36872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35409,7 +36937,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35470,7 +37002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35531,7 +37067,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35592,7 +37132,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35653,7 +37197,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35714,7 +37262,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35775,7 +37327,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35836,7 +37392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36019,7 +37579,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36080,7 +37644,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36263,7 +37831,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36324,7 +37896,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36385,7 +37961,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36446,7 +38026,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36507,7 +38091,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36568,7 +38156,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36690,7 +38282,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36812,7 +38408,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36873,7 +38473,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36934,7 +38538,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37056,7 +38664,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37117,7 +38729,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37178,7 +38794,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37239,7 +38859,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37300,7 +38924,11 @@
           <t>77.505.828-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37422,7 +39050,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37483,7 +39115,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37544,7 +39180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37605,7 +39245,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37666,7 +39310,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37849,7 +39497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37910,7 +39562,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37971,7 +39627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38032,7 +39692,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38154,7 +39818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38276,7 +39944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38520,7 +40192,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38642,7 +40318,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38947,7 +40627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39069,7 +40753,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39191,7 +40879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39313,7 +41005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39500,7 +41196,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39561,7 +41261,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39683,7 +41387,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39744,7 +41452,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39805,7 +41517,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39866,7 +41582,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39927,7 +41647,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39988,7 +41712,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40049,7 +41777,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40110,7 +41842,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40293,7 +42029,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40415,7 +42155,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40659,7 +42403,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40720,7 +42468,11 @@
           <t>77.618.373-3</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40842,7 +42594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40903,7 +42659,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41025,7 +42785,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41086,7 +42850,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41208,7 +42976,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41269,7 +43041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41330,7 +43106,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41391,7 +43171,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41696,7 +43480,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41757,7 +43545,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41818,7 +43610,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41879,7 +43675,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41940,7 +43740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42001,7 +43805,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42062,7 +43870,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42123,7 +43935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42245,7 +44061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42367,7 +44187,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42428,7 +44252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42550,7 +44378,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42611,7 +44443,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42733,7 +44569,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42794,7 +44634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42916,7 +44760,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43038,7 +44886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43099,7 +44951,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43160,7 +45016,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43221,7 +45081,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43282,7 +45146,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43343,7 +45211,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43404,7 +45276,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43465,7 +45341,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43526,7 +45406,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43587,7 +45471,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43709,7 +45597,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43770,7 +45662,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43953,7 +45849,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44014,7 +45914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44136,7 +46040,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44258,7 +46166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44319,7 +46231,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44380,7 +46296,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44441,7 +46361,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44502,7 +46426,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44563,7 +46491,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44624,7 +46556,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44685,7 +46621,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44746,7 +46686,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44807,7 +46751,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44990,7 +46938,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45051,7 +47003,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45173,7 +47129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45234,7 +47194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45295,7 +47259,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45356,7 +47324,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45417,7 +47389,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45478,7 +47454,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45539,7 +47519,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45600,7 +47584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45722,7 +47710,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45966,7 +47958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46027,7 +48023,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46271,7 +48271,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46332,7 +48336,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46393,7 +48401,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46454,7 +48466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46576,7 +48592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46637,7 +48657,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46698,7 +48722,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46759,7 +48787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46820,7 +48852,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46881,7 +48917,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46942,7 +48982,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47003,7 +49047,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47125,7 +49173,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47186,7 +49238,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47247,7 +49303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47308,7 +49368,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47369,7 +49433,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47491,7 +49559,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47552,7 +49624,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47613,7 +49689,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47735,7 +49815,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47979,7 +50063,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48040,7 +50128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48223,7 +50315,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48284,7 +50380,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48528,7 +50628,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48650,7 +50754,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48711,7 +50819,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48772,7 +50884,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48833,7 +50949,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48894,7 +51014,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48955,7 +51079,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49077,7 +51205,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49138,7 +51270,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49199,7 +51335,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49260,7 +51400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49321,7 +51465,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49443,7 +51591,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49748,7 +51900,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49809,7 +51965,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49870,7 +52030,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49931,7 +52095,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49992,7 +52160,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50053,7 +52225,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50114,7 +52290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50175,7 +52355,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50236,7 +52420,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50297,7 +52485,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50358,7 +52550,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50419,7 +52615,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50480,7 +52680,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50541,7 +52745,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50724,7 +52932,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50785,7 +52997,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50846,7 +53062,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50907,7 +53127,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51090,7 +53314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51212,7 +53440,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51273,7 +53505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51395,7 +53631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51517,7 +53757,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51578,7 +53822,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51639,7 +53887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51761,7 +54013,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51822,7 +54078,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51883,7 +54143,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52066,7 +54330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52127,7 +54395,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52188,7 +54460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52249,7 +54525,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52310,7 +54590,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L850" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52371,7 +54655,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52432,7 +54720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52493,7 +54785,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52554,7 +54850,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52615,7 +54915,11 @@
           <t>77.020.146-2</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52737,7 +55041,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52798,7 +55106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52859,7 +55171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52920,7 +55236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52981,7 +55301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53042,7 +55366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53103,7 +55431,11 @@
           <t>77.020.146-2</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L863" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53225,7 +55557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53347,7 +55683,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L867" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53591,7 +55931,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53652,7 +55996,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53713,7 +56061,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53957,7 +56309,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L877" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54018,7 +56374,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L878" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54384,7 +56744,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54628,7 +56992,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54689,7 +57057,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54750,7 +57122,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54933,7 +57309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54994,7 +57374,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55055,7 +57439,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L895" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55177,7 +57565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55238,7 +57630,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55299,7 +57695,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55360,7 +57760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55421,7 +57825,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55482,7 +57890,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55604,7 +58016,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55787,7 +58203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55848,7 +58268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L908" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55909,7 +58333,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55970,7 +58398,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56153,7 +58585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56214,7 +58650,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56275,7 +58715,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56458,7 +58902,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56580,7 +59028,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56641,7 +59093,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56763,7 +59219,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L923" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56824,7 +59284,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56885,7 +59349,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56946,7 +59414,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57007,7 +59479,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57129,7 +59605,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L929" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57190,7 +59670,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L930" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57251,7 +59735,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57312,7 +59800,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L932" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57373,7 +59865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57434,7 +59930,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57495,7 +59995,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57617,7 +60121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57739,7 +60247,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57800,7 +60312,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L940" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57922,7 +60438,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L942" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57983,7 +60503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58044,7 +60568,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L944" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58105,7 +60633,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L945" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58166,7 +60698,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58227,7 +60763,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58288,7 +60828,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58349,7 +60893,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58410,7 +60958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L950" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58471,7 +61023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L951" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58532,7 +61088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L952" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58593,7 +61153,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58654,7 +61218,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L954" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58776,7 +61344,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L956" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58837,7 +61409,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L957" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58898,7 +61474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K958" t="inlineStr"/>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L958" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59020,7 +61600,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L960" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59081,7 +61665,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L961" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59142,7 +61730,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L962" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59203,7 +61795,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L963" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59325,7 +61921,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L965" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59447,7 +62047,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59569,7 +62173,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L969" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59752,7 +62360,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K972" t="inlineStr"/>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L972" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59813,7 +62425,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60057,7 +62673,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L977" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60118,7 +62738,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr"/>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L978" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60179,7 +62803,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L979" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60301,7 +62929,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K981" t="inlineStr"/>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L981" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60362,7 +62994,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L982" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60423,7 +63059,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60484,7 +63124,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L984" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60545,7 +63189,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L985" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60728,7 +63376,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L988" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60850,7 +63502,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K990" t="inlineStr"/>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L990" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60911,7 +63567,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L991" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60972,7 +63632,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L992" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61033,7 +63697,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61094,7 +63762,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61155,7 +63827,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L995" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61216,7 +63892,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K996" t="inlineStr"/>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L996" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61338,7 +64018,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K998" t="inlineStr"/>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L998" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61399,7 +64083,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K999" t="inlineStr"/>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L999" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61460,7 +64148,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1000" t="inlineStr"/>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1000" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61521,7 +64213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1001" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61582,7 +64278,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K1002" t="inlineStr"/>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1002" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61643,7 +64343,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61765,7 +64469,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K1005" t="inlineStr"/>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1005" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62009,7 +64717,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1009" t="inlineStr"/>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1009" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62131,7 +64843,11 @@
           <t>78.188.383-2</t>
         </is>
       </c>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1011" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62253,7 +64969,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1013" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62497,7 +65217,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K1017" t="inlineStr"/>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L1017" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62558,7 +65282,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1018" t="inlineStr"/>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1018" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62741,7 +65469,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1021" t="inlineStr"/>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1021" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62802,7 +65534,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1022" t="inlineStr"/>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1022" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62863,7 +65599,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1023" t="inlineStr"/>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1023" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62985,7 +65725,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1025" t="inlineStr"/>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1025" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63046,7 +65790,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1026" t="inlineStr"/>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1026" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63107,7 +65855,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1027" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63168,7 +65920,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K1028" t="inlineStr"/>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1028" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63229,7 +65985,11 @@
           <t>77.916.035-1</t>
         </is>
       </c>
-      <c r="K1029" t="inlineStr"/>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L1029" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63290,7 +66050,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1030" t="inlineStr"/>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1030" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63351,7 +66115,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1031" t="inlineStr"/>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1031" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63412,7 +66180,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L1032" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63534,7 +66306,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1034" t="inlineStr"/>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1034" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63721,7 +66497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1037" t="inlineStr"/>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1037" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63782,7 +66562,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1038" t="inlineStr"/>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1038" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63904,7 +66688,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K1040" t="inlineStr"/>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1040" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63965,7 +66753,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K1041" t="inlineStr"/>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1041" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64026,7 +66818,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K1042" t="inlineStr"/>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1042" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64148,7 +66944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1044" t="inlineStr"/>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1044" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64270,7 +67070,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1046" t="inlineStr"/>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1046" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64392,7 +67196,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1048" t="inlineStr"/>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1048" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64453,7 +67261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1049" t="inlineStr"/>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1049" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64514,7 +67326,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K1050" t="inlineStr"/>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L1050" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64575,7 +67391,11 @@
           <t>77.909.444-8</t>
         </is>
       </c>
-      <c r="K1051" t="inlineStr"/>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1051" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64636,7 +67456,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1052" t="inlineStr"/>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1052" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64697,7 +67521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1053" t="inlineStr"/>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1053" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64880,7 +67708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1056" t="inlineStr"/>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1056" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64941,7 +67773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1057" t="inlineStr"/>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1057" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65002,7 +67838,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1058" t="inlineStr"/>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1058" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65063,7 +67903,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K1059" t="inlineStr"/>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1059" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65124,7 +67968,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1060" t="inlineStr"/>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1060" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65246,7 +68094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1062" t="inlineStr"/>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1062" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65307,7 +68159,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1063" t="inlineStr"/>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1063" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65429,7 +68285,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1065" t="inlineStr"/>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1065" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65551,7 +68411,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K1067" t="inlineStr"/>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1067" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65673,7 +68537,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1069" t="inlineStr"/>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1069" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65734,7 +68602,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1070" t="inlineStr"/>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1070" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65795,7 +68667,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1071" t="inlineStr"/>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1071" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66039,7 +68915,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1075" t="inlineStr"/>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1075" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66100,7 +68980,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1076" t="inlineStr"/>
+      <c r="K1076" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1076" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66344,7 +69228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1080" t="inlineStr"/>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1080" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66466,7 +69354,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1082" t="inlineStr"/>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1082" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66588,7 +69480,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1084" t="inlineStr"/>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1084" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66649,7 +69545,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1085" t="inlineStr"/>
+      <c r="K1085" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1085" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66710,7 +69610,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1086" t="inlineStr"/>
+      <c r="K1086" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1086" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66893,7 +69797,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K1089" t="inlineStr"/>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1089" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67015,7 +69923,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1091" t="inlineStr"/>
+      <c r="K1091" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1091" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67137,7 +70049,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1093" t="inlineStr"/>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1093" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67198,7 +70114,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1094" t="inlineStr"/>
+      <c r="K1094" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1094" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67259,7 +70179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1095" t="inlineStr"/>
+      <c r="K1095" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1095" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67320,7 +70244,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1096" t="inlineStr"/>
+      <c r="K1096" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1096" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67442,7 +70370,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1098" t="inlineStr"/>
+      <c r="K1098" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1098" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67503,7 +70435,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1099" t="inlineStr"/>
+      <c r="K1099" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1099" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67564,7 +70500,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K1100" t="inlineStr"/>
+      <c r="K1100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67625,7 +70565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1101" t="inlineStr"/>
+      <c r="K1101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67686,7 +70630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1102" t="inlineStr"/>
+      <c r="K1102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67747,7 +70695,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K1103" t="inlineStr"/>
+      <c r="K1103" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1103" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
@@ -883,7 +883,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1196,7 +1200,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1517,7 +1525,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1578,7 +1590,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2220,7 +2236,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2468,7 +2488,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2594,7 +2618,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3293,7 +3321,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3866,7 +3898,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4760,7 +4796,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6426,7 +6466,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7064,7 +7108,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7690,7 +7738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8068,7 +8120,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9738,7 +9794,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10055,7 +10115,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10311,7 +10375,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10498,7 +10566,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10624,7 +10696,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12420,7 +12496,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12676,7 +12756,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14988,7 +15072,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15236,7 +15324,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15996,7 +16088,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16374,7 +16470,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16756,7 +16856,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16882,7 +16986,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +17754,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17963,7 +18075,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18337,7 +18453,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18463,7 +18583,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19918,7 +20042,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19979,7 +20107,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20235,7 +20367,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21003,7 +21139,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21385,7 +21525,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23459,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +23654,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24274,7 +24426,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24591,7 +24747,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26578,7 +26738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26899,7 +27063,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27082,7 +27250,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27399,7 +27571,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28797,7 +28973,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29435,7 +29615,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31418,7 +31602,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31544,7 +31732,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31605,7 +31797,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31731,7 +31927,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31857,7 +32057,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32422,7 +32626,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32930,7 +33138,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33056,7 +33268,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33117,7 +33333,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33824,7 +34044,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34015,7 +34239,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34336,7 +34564,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35238,7 +35470,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35608,7 +35844,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35669,7 +35909,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35730,7 +35974,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35791,7 +36039,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36555,7 +36807,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36811,7 +37067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37457,7 +37717,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37518,7 +37782,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37709,7 +37977,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37770,7 +38042,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38221,7 +38497,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38347,7 +38627,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38603,7 +38887,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39436,7 +39724,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40131,7 +40423,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40383,7 +40679,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40505,7 +40805,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40566,7 +40870,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40818,7 +41126,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41907,7 +42219,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42724,7 +43040,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43236,7 +43556,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43358,7 +43682,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44508,7 +44836,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44825,7 +45157,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45536,7 +45872,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45727,7 +46067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45788,7 +46132,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45979,7 +46327,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46816,7 +47168,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46877,7 +47233,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47897,7 +48257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49880,7 +50244,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50445,7 +50813,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51839,7 +52211,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53192,7 +53568,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53253,7 +53633,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55496,7 +55880,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55622,7 +56010,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55809,7 +56201,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56126,7 +56522,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56248,7 +56648,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56439,7 +56843,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56500,7 +56908,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57504,7 +57916,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58142,7 +58558,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58463,7 +58883,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58841,7 +59265,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59158,7 +59586,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60186,7 +60618,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61539,7 +61975,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61860,7 +62300,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L964" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62238,7 +62682,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K970" t="inlineStr"/>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L970" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62612,7 +63060,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62868,7 +63320,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63254,7 +63710,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L986" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63441,7 +63901,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L989" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64408,7 +64872,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1004" t="inlineStr"/>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1004" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64595,7 +65063,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1007" t="inlineStr"/>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1007" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65347,7 +65819,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1019" t="inlineStr"/>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1019" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65408,7 +65884,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1020" t="inlineStr"/>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1020" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65664,7 +66144,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1024" t="inlineStr"/>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1024" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66371,7 +66855,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1035" t="inlineStr"/>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1035" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68033,7 +68521,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1061" t="inlineStr"/>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1061" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68732,7 +69224,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1072" t="inlineStr"/>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1072" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68793,7 +69289,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1073" t="inlineStr"/>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1073" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69045,7 +69545,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1077" t="inlineStr"/>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1077" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69293,7 +69797,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1081" t="inlineStr"/>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1081" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69419,7 +69927,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1083" t="inlineStr"/>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1083" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69675,7 +70187,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1087" t="inlineStr"/>
+      <c r="K1087" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1087" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70309,7 +70825,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1097" t="inlineStr"/>
+      <c r="K1097" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1097" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/mar-2026.xlsx
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -49383,7 +49383,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
@@ -55141,7 +55141,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
@@ -55722,7 +55722,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
@@ -56945,7 +56945,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
@@ -62845,7 +62845,7 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
@@ -68363,7 +68363,7 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
@@ -69704,7 +69704,7 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
